--- a/reports/module-migration-sunset-backlog/2026-07-27/MODULE_DATA_LAYER_MIGRATION_BACKLOG.xlsx
+++ b/reports/module-migration-sunset-backlog/2026-07-27/MODULE_DATA_LAYER_MIGRATION_BACKLOG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration Backlog" sheetId="1" r:id="R833780e17b364b9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Migration Backlog" sheetId="1" r:id="Rf366180bcf3a433b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -327,6 +327,7 @@
     <x:col min="17" max="17" width="42" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="42" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="42" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
@@ -352,39 +353,42 @@
         <x:v>target_operational_owner</x:v>
       </x:c>
       <x:c r="H1" s="9" t="str">
-        <x:v>canonical_promotion_target</x:v>
+        <x:v>provisional_canonical_object_family</x:v>
       </x:c>
       <x:c r="I1" s="9" t="str">
+        <x:v>mapping_confidence</x:v>
+      </x:c>
+      <x:c r="J1" s="9" t="str">
         <x:v>target_consumption_projection</x:v>
       </x:c>
-      <x:c r="J1" s="9" t="str">
+      <x:c r="K1" s="9" t="str">
         <x:v>migration_method</x:v>
       </x:c>
-      <x:c r="K1" s="9" t="str">
+      <x:c r="L1" s="9" t="str">
         <x:v>historical_backfill</x:v>
       </x:c>
-      <x:c r="L1" s="9" t="str">
+      <x:c r="M1" s="9" t="str">
         <x:v>dual_run_requirement</x:v>
       </x:c>
-      <x:c r="M1" s="9" t="str">
+      <x:c r="N1" s="9" t="str">
         <x:v>reconciliation_rule</x:v>
       </x:c>
-      <x:c r="N1" s="9" t="str">
+      <x:c r="O1" s="9" t="str">
         <x:v>cutover_dependency</x:v>
       </x:c>
-      <x:c r="O1" s="9" t="str">
+      <x:c r="P1" s="9" t="str">
         <x:v>rollback_path</x:v>
       </x:c>
-      <x:c r="P1" s="9" t="str">
+      <x:c r="Q1" s="9" t="str">
         <x:v>read_only_observation_period</x:v>
       </x:c>
-      <x:c r="Q1" s="9" t="str">
+      <x:c r="R1" s="9" t="str">
         <x:v>archive_requirement</x:v>
       </x:c>
-      <x:c r="R1" s="9" t="str">
+      <x:c r="S1" s="9" t="str">
         <x:v>drop_authorization</x:v>
       </x:c>
-      <x:c r="S1" s="9" t="str">
+      <x:c r="T1" s="9" t="str">
         <x:v>status</x:v>
       </x:c>
     </x:row>
@@ -413,35 +417,38 @@
       <x:c r="H2" s="5" t="str">
         <x:v>governance.object_identity_map</x:v>
       </x:c>
-      <x:c r="I2" s="5" t="str"/>
-      <x:c r="J2" s="5" t="str">
+      <x:c r="I2" s="5" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="J2" s="5" t="str"/>
+      <x:c r="K2" s="5" t="str">
         <x:v>Design and approve before any module migration</x:v>
       </x:c>
-      <x:c r="K2" s="5" t="str">
+      <x:c r="L2" s="5" t="str">
         <x:v>none until identity policy is approved</x:v>
       </x:c>
-      <x:c r="L2" s="5" t="str">
+      <x:c r="M2" s="5" t="str">
         <x:v>Identity shadow mode before any read cutover</x:v>
       </x:c>
-      <x:c r="M2" s="5" t="str">
+      <x:c r="N2" s="5" t="str">
         <x:v>Every local object link has tenant, type, confidence, review state, and history</x:v>
       </x:c>
-      <x:c r="N2" s="5" t="str">
+      <x:c r="O2" s="5" t="str">
         <x:v>Healthcare certified Knowledge Baseline</x:v>
       </x:c>
-      <x:c r="O2" s="5" t="str">
+      <x:c r="P2" s="5" t="str">
         <x:v>Do not use canonical identity reads until approved</x:v>
       </x:c>
-      <x:c r="P2" s="5" t="str">
+      <x:c r="Q2" s="5" t="str">
         <x:v>Not applicable</x:v>
       </x:c>
-      <x:c r="Q2" s="5" t="str">
+      <x:c r="R2" s="5" t="str">
         <x:v>Identity map changes are append-only</x:v>
       </x:c>
-      <x:c r="R2" s="5" t="str">
+      <x:c r="S2" s="5" t="str">
         <x:v>Not applicable</x:v>
       </x:c>
-      <x:c r="S2" s="5" t="str">
+      <x:c r="T2" s="5" t="str">
         <x:v>foundation_required</x:v>
       </x:c>
     </x:row>
@@ -470,35 +477,38 @@
       <x:c r="H3" s="5" t="str">
         <x:v>governance.module_publication_outbox</x:v>
       </x:c>
-      <x:c r="I3" s="5" t="str"/>
-      <x:c r="J3" s="5" t="str">
+      <x:c r="I3" s="5" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="J3" s="5" t="str"/>
+      <x:c r="K3" s="5" t="str">
         <x:v>Implement after Healthcare publication lifecycle proves out</x:v>
       </x:c>
-      <x:c r="K3" s="5" t="str">
+      <x:c r="L3" s="5" t="str">
         <x:v>none before approved replay strategy</x:v>
       </x:c>
-      <x:c r="L3" s="5" t="str">
+      <x:c r="M3" s="5" t="str">
         <x:v>Required with old direct-write paths</x:v>
       </x:c>
-      <x:c r="M3" s="5" t="str">
+      <x:c r="N3" s="5" t="str">
         <x:v>Outbox event count equals accepted domain event count by tenant/module/object family</x:v>
       </x:c>
-      <x:c r="N3" s="5" t="str">
+      <x:c r="O3" s="5" t="str">
         <x:v>Business-event telemetry active</x:v>
       </x:c>
-      <x:c r="O3" s="5" t="str">
+      <x:c r="P3" s="5" t="str">
         <x:v>Stop outbox processing; retain domain workflow tables</x:v>
       </x:c>
-      <x:c r="P3" s="5" t="str">
+      <x:c r="Q3" s="5" t="str">
         <x:v>30 days before write primary</x:v>
       </x:c>
-      <x:c r="Q3" s="5" t="str">
+      <x:c r="R3" s="5" t="str">
         <x:v>Outbox events retained as audit stream</x:v>
       </x:c>
-      <x:c r="R3" s="5" t="str">
+      <x:c r="S3" s="5" t="str">
         <x:v>Not applicable</x:v>
       </x:c>
-      <x:c r="S3" s="5" t="str">
+      <x:c r="T3" s="5" t="str">
         <x:v>foundation_required</x:v>
       </x:c>
     </x:row>
@@ -528,36 +538,39 @@
         <x:v>knowledge.metric_definition</x:v>
       </x:c>
       <x:c r="I4" s="5" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="J4" s="5" t="str">
         <x:v>consumption.metric_observation_*</x:v>
       </x:c>
-      <x:c r="J4" s="5" t="str">
+      <x:c r="K4" s="5" t="str">
         <x:v>Separate definition from observation; publish formula versions before observations</x:v>
       </x:c>
-      <x:c r="K4" s="5" t="str">
+      <x:c r="L4" s="5" t="str">
         <x:v>Backfill current definitions first, then observations</x:v>
       </x:c>
-      <x:c r="L4" s="5" t="str">
+      <x:c r="M4" s="5" t="str">
         <x:v>Required for every headline number</x:v>
       </x:c>
-      <x:c r="M4" s="5" t="str">
+      <x:c r="N4" s="5" t="str">
         <x:v>Formula, period, unit, basis, source, and value parity</x:v>
       </x:c>
-      <x:c r="N4" s="5" t="str">
+      <x:c r="O4" s="5" t="str">
         <x:v>Metric owner attestation and lineage validation</x:v>
       </x:c>
-      <x:c r="O4" s="5" t="str">
+      <x:c r="P4" s="5" t="str">
         <x:v>Revert consumers to module-specific calculation while keeping shared definitions candidate</x:v>
       </x:c>
-      <x:c r="P4" s="5" t="str">
+      <x:c r="Q4" s="5" t="str">
         <x:v>60 days</x:v>
       </x:c>
-      <x:c r="Q4" s="5" t="str">
+      <x:c r="R4" s="5" t="str">
         <x:v>Preserve old formula outputs for reconciliation</x:v>
       </x:c>
-      <x:c r="R4" s="5" t="str">
+      <x:c r="S4" s="5" t="str">
         <x:v>Explicit later approval</x:v>
       </x:c>
-      <x:c r="S4" s="5" t="str">
+      <x:c r="T4" s="5" t="str">
         <x:v>foundation_required</x:v>
       </x:c>
     </x:row>
@@ -585,34 +598,35 @@
       </x:c>
       <x:c r="H5" s="5" t="str"/>
       <x:c r="I5" s="5" t="str"/>
-      <x:c r="J5" s="5" t="str">
+      <x:c r="J5" s="5" t="str"/>
+      <x:c r="K5" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K5" s="5" t="str">
+      <x:c r="L5" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L5" s="5" t="str">
+      <x:c r="M5" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M5" s="5" t="str">
+      <x:c r="N5" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N5" s="5" t="str">
+      <x:c r="O5" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O5" s="5" t="str">
+      <x:c r="P5" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P5" s="5" t="str">
+      <x:c r="Q5" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q5" s="5" t="str">
+      <x:c r="R5" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R5" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S5" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T5" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -640,34 +654,35 @@
       </x:c>
       <x:c r="H6" s="5" t="str"/>
       <x:c r="I6" s="5" t="str"/>
-      <x:c r="J6" s="5" t="str">
+      <x:c r="J6" s="5" t="str"/>
+      <x:c r="K6" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K6" s="5" t="str">
+      <x:c r="L6" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L6" s="5" t="str">
+      <x:c r="M6" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M6" s="5" t="str">
+      <x:c r="N6" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N6" s="5" t="str">
+      <x:c r="O6" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O6" s="5" t="str">
+      <x:c r="P6" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P6" s="5" t="str">
+      <x:c r="Q6" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q6" s="5" t="str">
+      <x:c r="R6" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R6" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S6" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T6" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -695,34 +710,35 @@
       </x:c>
       <x:c r="H7" s="5" t="str"/>
       <x:c r="I7" s="5" t="str"/>
-      <x:c r="J7" s="5" t="str">
+      <x:c r="J7" s="5" t="str"/>
+      <x:c r="K7" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K7" s="5" t="str">
+      <x:c r="L7" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L7" s="5" t="str">
+      <x:c r="M7" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M7" s="5" t="str">
+      <x:c r="N7" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N7" s="5" t="str">
+      <x:c r="O7" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O7" s="5" t="str">
+      <x:c r="P7" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P7" s="5" t="str">
+      <x:c r="Q7" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q7" s="5" t="str">
+      <x:c r="R7" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R7" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S7" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T7" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -750,34 +766,35 @@
       </x:c>
       <x:c r="H8" s="5" t="str"/>
       <x:c r="I8" s="5" t="str"/>
-      <x:c r="J8" s="5" t="str">
+      <x:c r="J8" s="5" t="str"/>
+      <x:c r="K8" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K8" s="5" t="str">
+      <x:c r="L8" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L8" s="5" t="str">
+      <x:c r="M8" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M8" s="5" t="str">
+      <x:c r="N8" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N8" s="5" t="str">
+      <x:c r="O8" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O8" s="5" t="str">
+      <x:c r="P8" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P8" s="5" t="str">
+      <x:c r="Q8" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q8" s="5" t="str">
+      <x:c r="R8" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R8" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S8" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T8" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -805,34 +822,35 @@
       </x:c>
       <x:c r="H9" s="5" t="str"/>
       <x:c r="I9" s="5" t="str"/>
-      <x:c r="J9" s="5" t="str">
+      <x:c r="J9" s="5" t="str"/>
+      <x:c r="K9" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K9" s="5" t="str">
+      <x:c r="L9" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L9" s="5" t="str">
+      <x:c r="M9" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M9" s="5" t="str">
+      <x:c r="N9" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N9" s="5" t="str">
+      <x:c r="O9" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O9" s="5" t="str">
+      <x:c r="P9" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P9" s="5" t="str">
+      <x:c r="Q9" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q9" s="5" t="str">
+      <x:c r="R9" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R9" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S9" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T9" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -860,34 +878,35 @@
       </x:c>
       <x:c r="H10" s="5" t="str"/>
       <x:c r="I10" s="5" t="str"/>
-      <x:c r="J10" s="5" t="str">
+      <x:c r="J10" s="5" t="str"/>
+      <x:c r="K10" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K10" s="5" t="str">
+      <x:c r="L10" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L10" s="5" t="str">
+      <x:c r="M10" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M10" s="5" t="str">
+      <x:c r="N10" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N10" s="5" t="str">
+      <x:c r="O10" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O10" s="5" t="str">
+      <x:c r="P10" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P10" s="5" t="str">
+      <x:c r="Q10" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q10" s="5" t="str">
+      <x:c r="R10" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R10" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S10" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T10" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -915,34 +934,35 @@
       </x:c>
       <x:c r="H11" s="5" t="str"/>
       <x:c r="I11" s="5" t="str"/>
-      <x:c r="J11" s="5" t="str">
+      <x:c r="J11" s="5" t="str"/>
+      <x:c r="K11" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K11" s="5" t="str">
+      <x:c r="L11" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L11" s="5" t="str">
+      <x:c r="M11" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M11" s="5" t="str">
+      <x:c r="N11" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N11" s="5" t="str">
+      <x:c r="O11" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O11" s="5" t="str">
+      <x:c r="P11" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P11" s="5" t="str">
+      <x:c r="Q11" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q11" s="5" t="str">
+      <x:c r="R11" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R11" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S11" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T11" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -970,34 +990,35 @@
       </x:c>
       <x:c r="H12" s="5" t="str"/>
       <x:c r="I12" s="5" t="str"/>
-      <x:c r="J12" s="5" t="str">
+      <x:c r="J12" s="5" t="str"/>
+      <x:c r="K12" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K12" s="5" t="str">
+      <x:c r="L12" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L12" s="5" t="str">
+      <x:c r="M12" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M12" s="5" t="str">
+      <x:c r="N12" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N12" s="5" t="str">
+      <x:c r="O12" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O12" s="5" t="str">
+      <x:c r="P12" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P12" s="5" t="str">
+      <x:c r="Q12" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q12" s="5" t="str">
+      <x:c r="R12" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R12" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S12" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T12" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -1025,34 +1046,35 @@
       </x:c>
       <x:c r="H13" s="5" t="str"/>
       <x:c r="I13" s="5" t="str"/>
-      <x:c r="J13" s="5" t="str">
+      <x:c r="J13" s="5" t="str"/>
+      <x:c r="K13" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K13" s="5" t="str">
+      <x:c r="L13" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L13" s="5" t="str">
+      <x:c r="M13" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M13" s="5" t="str">
+      <x:c r="N13" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N13" s="5" t="str">
+      <x:c r="O13" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O13" s="5" t="str">
+      <x:c r="P13" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P13" s="5" t="str">
+      <x:c r="Q13" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q13" s="5" t="str">
+      <x:c r="R13" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R13" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S13" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T13" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -1080,34 +1102,35 @@
       </x:c>
       <x:c r="H14" s="5" t="str"/>
       <x:c r="I14" s="5" t="str"/>
-      <x:c r="J14" s="5" t="str">
+      <x:c r="J14" s="5" t="str"/>
+      <x:c r="K14" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K14" s="5" t="str">
+      <x:c r="L14" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L14" s="5" t="str">
+      <x:c r="M14" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M14" s="5" t="str">
+      <x:c r="N14" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N14" s="5" t="str">
+      <x:c r="O14" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O14" s="5" t="str">
+      <x:c r="P14" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P14" s="5" t="str">
+      <x:c r="Q14" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q14" s="5" t="str">
+      <x:c r="R14" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R14" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S14" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T14" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -1135,34 +1158,35 @@
       </x:c>
       <x:c r="H15" s="5" t="str"/>
       <x:c r="I15" s="5" t="str"/>
-      <x:c r="J15" s="5" t="str">
+      <x:c r="J15" s="5" t="str"/>
+      <x:c r="K15" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K15" s="5" t="str">
+      <x:c r="L15" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L15" s="5" t="str">
+      <x:c r="M15" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M15" s="5" t="str">
+      <x:c r="N15" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N15" s="5" t="str">
+      <x:c r="O15" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O15" s="5" t="str">
+      <x:c r="P15" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P15" s="5" t="str">
+      <x:c r="Q15" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q15" s="5" t="str">
+      <x:c r="R15" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R15" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S15" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T15" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -1190,34 +1214,35 @@
       </x:c>
       <x:c r="H16" s="5" t="str"/>
       <x:c r="I16" s="5" t="str"/>
-      <x:c r="J16" s="5" t="str">
+      <x:c r="J16" s="5" t="str"/>
+      <x:c r="K16" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K16" s="5" t="str">
+      <x:c r="L16" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L16" s="5" t="str">
+      <x:c r="M16" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M16" s="5" t="str">
+      <x:c r="N16" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N16" s="5" t="str">
+      <x:c r="O16" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O16" s="5" t="str">
+      <x:c r="P16" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P16" s="5" t="str">
+      <x:c r="Q16" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q16" s="5" t="str">
+      <x:c r="R16" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R16" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S16" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T16" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -1245,34 +1270,35 @@
       </x:c>
       <x:c r="H17" s="5" t="str"/>
       <x:c r="I17" s="5" t="str"/>
-      <x:c r="J17" s="5" t="str">
+      <x:c r="J17" s="5" t="str"/>
+      <x:c r="K17" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K17" s="5" t="str">
+      <x:c r="L17" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L17" s="5" t="str">
+      <x:c r="M17" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M17" s="5" t="str">
+      <x:c r="N17" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N17" s="5" t="str">
+      <x:c r="O17" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O17" s="5" t="str">
+      <x:c r="P17" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P17" s="5" t="str">
+      <x:c r="Q17" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q17" s="5" t="str">
+      <x:c r="R17" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R17" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S17" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T17" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -1300,34 +1326,35 @@
       </x:c>
       <x:c r="H18" s="5" t="str"/>
       <x:c r="I18" s="5" t="str"/>
-      <x:c r="J18" s="5" t="str">
+      <x:c r="J18" s="5" t="str"/>
+      <x:c r="K18" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K18" s="5" t="str">
+      <x:c r="L18" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L18" s="5" t="str">
+      <x:c r="M18" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M18" s="5" t="str">
+      <x:c r="N18" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N18" s="5" t="str">
+      <x:c r="O18" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O18" s="5" t="str">
+      <x:c r="P18" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P18" s="5" t="str">
+      <x:c r="Q18" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q18" s="5" t="str">
+      <x:c r="R18" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R18" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S18" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T18" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -1355,34 +1382,35 @@
       </x:c>
       <x:c r="H19" s="5" t="str"/>
       <x:c r="I19" s="5" t="str"/>
-      <x:c r="J19" s="5" t="str">
+      <x:c r="J19" s="5" t="str"/>
+      <x:c r="K19" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K19" s="5" t="str">
+      <x:c r="L19" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L19" s="5" t="str">
+      <x:c r="M19" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M19" s="5" t="str">
+      <x:c r="N19" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N19" s="5" t="str">
+      <x:c r="O19" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O19" s="5" t="str">
+      <x:c r="P19" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P19" s="5" t="str">
+      <x:c r="Q19" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q19" s="5" t="str">
+      <x:c r="R19" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R19" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S19" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T19" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -1410,34 +1438,35 @@
       </x:c>
       <x:c r="H20" s="5" t="str"/>
       <x:c r="I20" s="5" t="str"/>
-      <x:c r="J20" s="5" t="str">
+      <x:c r="J20" s="5" t="str"/>
+      <x:c r="K20" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K20" s="5" t="str">
+      <x:c r="L20" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L20" s="5" t="str">
+      <x:c r="M20" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M20" s="5" t="str">
+      <x:c r="N20" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N20" s="5" t="str">
+      <x:c r="O20" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O20" s="5" t="str">
+      <x:c r="P20" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P20" s="5" t="str">
+      <x:c r="Q20" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q20" s="5" t="str">
+      <x:c r="R20" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R20" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S20" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T20" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -1466,35 +1495,38 @@
       <x:c r="H21" s="5" t="str">
         <x:v>knowledge.evidence</x:v>
       </x:c>
-      <x:c r="I21" s="5" t="str"/>
-      <x:c r="J21" s="5" t="str">
+      <x:c r="I21" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J21" s="5" t="str"/>
+      <x:c r="K21" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K21" s="5" t="str">
+      <x:c r="L21" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L21" s="5" t="str">
+      <x:c r="M21" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M21" s="5" t="str">
+      <x:c r="N21" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N21" s="5" t="str">
+      <x:c r="O21" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O21" s="5" t="str">
+      <x:c r="P21" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P21" s="5" t="str">
+      <x:c r="Q21" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q21" s="5" t="str">
+      <x:c r="R21" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R21" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S21" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T21" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -1522,34 +1554,35 @@
       </x:c>
       <x:c r="H22" s="5" t="str"/>
       <x:c r="I22" s="5" t="str"/>
-      <x:c r="J22" s="5" t="str">
+      <x:c r="J22" s="5" t="str"/>
+      <x:c r="K22" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K22" s="5" t="str">
+      <x:c r="L22" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L22" s="5" t="str">
+      <x:c r="M22" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M22" s="5" t="str">
+      <x:c r="N22" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N22" s="5" t="str">
+      <x:c r="O22" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O22" s="5" t="str">
+      <x:c r="P22" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P22" s="5" t="str">
+      <x:c r="Q22" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q22" s="5" t="str">
+      <x:c r="R22" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R22" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S22" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T22" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -1578,35 +1611,38 @@
       <x:c r="H23" s="5" t="str">
         <x:v>knowledge.evidence</x:v>
       </x:c>
-      <x:c r="I23" s="5" t="str"/>
-      <x:c r="J23" s="5" t="str">
+      <x:c r="I23" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J23" s="5" t="str"/>
+      <x:c r="K23" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K23" s="5" t="str">
+      <x:c r="L23" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L23" s="5" t="str">
+      <x:c r="M23" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M23" s="5" t="str">
+      <x:c r="N23" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N23" s="5" t="str">
+      <x:c r="O23" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O23" s="5" t="str">
+      <x:c r="P23" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P23" s="5" t="str">
+      <x:c r="Q23" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q23" s="5" t="str">
+      <x:c r="R23" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R23" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S23" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T23" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -1634,34 +1670,35 @@
       </x:c>
       <x:c r="H24" s="5" t="str"/>
       <x:c r="I24" s="5" t="str"/>
-      <x:c r="J24" s="5" t="str">
+      <x:c r="J24" s="5" t="str"/>
+      <x:c r="K24" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K24" s="5" t="str">
+      <x:c r="L24" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L24" s="5" t="str">
+      <x:c r="M24" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M24" s="5" t="str">
+      <x:c r="N24" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N24" s="5" t="str">
+      <x:c r="O24" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O24" s="5" t="str">
+      <x:c r="P24" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P24" s="5" t="str">
+      <x:c r="Q24" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q24" s="5" t="str">
+      <x:c r="R24" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R24" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S24" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T24" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -1689,34 +1726,35 @@
       </x:c>
       <x:c r="H25" s="5" t="str"/>
       <x:c r="I25" s="5" t="str"/>
-      <x:c r="J25" s="5" t="str">
+      <x:c r="J25" s="5" t="str"/>
+      <x:c r="K25" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K25" s="5" t="str">
+      <x:c r="L25" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L25" s="5" t="str">
+      <x:c r="M25" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M25" s="5" t="str">
+      <x:c r="N25" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N25" s="5" t="str">
+      <x:c r="O25" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O25" s="5" t="str">
+      <x:c r="P25" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P25" s="5" t="str">
+      <x:c r="Q25" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q25" s="5" t="str">
+      <x:c r="R25" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R25" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S25" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T25" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -1744,34 +1782,35 @@
       </x:c>
       <x:c r="H26" s="5" t="str"/>
       <x:c r="I26" s="5" t="str"/>
-      <x:c r="J26" s="5" t="str">
+      <x:c r="J26" s="5" t="str"/>
+      <x:c r="K26" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K26" s="5" t="str">
+      <x:c r="L26" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L26" s="5" t="str">
+      <x:c r="M26" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M26" s="5" t="str">
+      <x:c r="N26" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N26" s="5" t="str">
+      <x:c r="O26" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O26" s="5" t="str">
+      <x:c r="P26" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P26" s="5" t="str">
+      <x:c r="Q26" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q26" s="5" t="str">
+      <x:c r="R26" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R26" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S26" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T26" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -1799,34 +1838,35 @@
       </x:c>
       <x:c r="H27" s="5" t="str"/>
       <x:c r="I27" s="5" t="str"/>
-      <x:c r="J27" s="5" t="str">
+      <x:c r="J27" s="5" t="str"/>
+      <x:c r="K27" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K27" s="5" t="str">
+      <x:c r="L27" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L27" s="5" t="str">
+      <x:c r="M27" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M27" s="5" t="str">
+      <x:c r="N27" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N27" s="5" t="str">
+      <x:c r="O27" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O27" s="5" t="str">
+      <x:c r="P27" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P27" s="5" t="str">
+      <x:c r="Q27" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q27" s="5" t="str">
+      <x:c r="R27" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R27" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S27" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T27" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -1855,35 +1895,38 @@
       <x:c r="H28" s="5" t="str">
         <x:v>knowledge.evidence_chunk</x:v>
       </x:c>
-      <x:c r="I28" s="5" t="str"/>
-      <x:c r="J28" s="5" t="str">
+      <x:c r="I28" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J28" s="5" t="str"/>
+      <x:c r="K28" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K28" s="5" t="str">
+      <x:c r="L28" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L28" s="5" t="str">
+      <x:c r="M28" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M28" s="5" t="str">
+      <x:c r="N28" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N28" s="5" t="str">
+      <x:c r="O28" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O28" s="5" t="str">
+      <x:c r="P28" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P28" s="5" t="str">
+      <x:c r="Q28" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q28" s="5" t="str">
+      <x:c r="R28" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R28" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S28" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T28" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -1912,35 +1955,38 @@
       <x:c r="H29" s="5" t="str">
         <x:v>knowledge.fact</x:v>
       </x:c>
-      <x:c r="I29" s="5" t="str"/>
-      <x:c r="J29" s="5" t="str">
+      <x:c r="I29" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J29" s="5" t="str"/>
+      <x:c r="K29" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K29" s="5" t="str">
+      <x:c r="L29" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L29" s="5" t="str">
+      <x:c r="M29" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M29" s="5" t="str">
+      <x:c r="N29" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N29" s="5" t="str">
+      <x:c r="O29" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O29" s="5" t="str">
+      <x:c r="P29" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P29" s="5" t="str">
+      <x:c r="Q29" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q29" s="5" t="str">
+      <x:c r="R29" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R29" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S29" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T29" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -1968,34 +2014,35 @@
       </x:c>
       <x:c r="H30" s="5" t="str"/>
       <x:c r="I30" s="5" t="str"/>
-      <x:c r="J30" s="5" t="str">
+      <x:c r="J30" s="5" t="str"/>
+      <x:c r="K30" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K30" s="5" t="str">
+      <x:c r="L30" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L30" s="5" t="str">
+      <x:c r="M30" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M30" s="5" t="str">
+      <x:c r="N30" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N30" s="5" t="str">
+      <x:c r="O30" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O30" s="5" t="str">
+      <x:c r="P30" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P30" s="5" t="str">
+      <x:c r="Q30" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q30" s="5" t="str">
+      <x:c r="R30" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R30" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S30" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T30" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -2023,34 +2070,35 @@
       </x:c>
       <x:c r="H31" s="5" t="str"/>
       <x:c r="I31" s="5" t="str"/>
-      <x:c r="J31" s="5" t="str">
+      <x:c r="J31" s="5" t="str"/>
+      <x:c r="K31" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K31" s="5" t="str">
+      <x:c r="L31" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L31" s="5" t="str">
+      <x:c r="M31" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M31" s="5" t="str">
+      <x:c r="N31" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N31" s="5" t="str">
+      <x:c r="O31" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O31" s="5" t="str">
+      <x:c r="P31" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P31" s="5" t="str">
+      <x:c r="Q31" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q31" s="5" t="str">
+      <x:c r="R31" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R31" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S31" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T31" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -2078,34 +2126,35 @@
       </x:c>
       <x:c r="H32" s="5" t="str"/>
       <x:c r="I32" s="5" t="str"/>
-      <x:c r="J32" s="5" t="str">
+      <x:c r="J32" s="5" t="str"/>
+      <x:c r="K32" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K32" s="5" t="str">
+      <x:c r="L32" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L32" s="5" t="str">
+      <x:c r="M32" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M32" s="5" t="str">
+      <x:c r="N32" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N32" s="5" t="str">
+      <x:c r="O32" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O32" s="5" t="str">
+      <x:c r="P32" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P32" s="5" t="str">
+      <x:c r="Q32" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q32" s="5" t="str">
+      <x:c r="R32" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R32" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S32" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T32" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -2132,37 +2181,40 @@
         <x:v>Source until publication</x:v>
       </x:c>
       <x:c r="H33" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
-      </x:c>
-      <x:c r="I33" s="5" t="str"/>
-      <x:c r="J33" s="5" t="str">
+        <x:v>knowledge.evidence_manifest</x:v>
+      </x:c>
+      <x:c r="I33" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J33" s="5" t="str"/>
+      <x:c r="K33" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K33" s="5" t="str">
+      <x:c r="L33" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L33" s="5" t="str">
+      <x:c r="M33" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M33" s="5" t="str">
+      <x:c r="N33" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N33" s="5" t="str">
+      <x:c r="O33" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O33" s="5" t="str">
+      <x:c r="P33" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P33" s="5" t="str">
+      <x:c r="Q33" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q33" s="5" t="str">
+      <x:c r="R33" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R33" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S33" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T33" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -2189,37 +2241,40 @@
         <x:v>Source until publication</x:v>
       </x:c>
       <x:c r="H34" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
-      </x:c>
-      <x:c r="I34" s="5" t="str"/>
-      <x:c r="J34" s="5" t="str">
+        <x:v>knowledge.metric_observation</x:v>
+      </x:c>
+      <x:c r="I34" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J34" s="5" t="str"/>
+      <x:c r="K34" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K34" s="5" t="str">
+      <x:c r="L34" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L34" s="5" t="str">
+      <x:c r="M34" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M34" s="5" t="str">
+      <x:c r="N34" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N34" s="5" t="str">
+      <x:c r="O34" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O34" s="5" t="str">
+      <x:c r="P34" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P34" s="5" t="str">
+      <x:c r="Q34" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q34" s="5" t="str">
+      <x:c r="R34" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R34" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S34" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T34" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -2246,37 +2301,40 @@
         <x:v>Source until publication</x:v>
       </x:c>
       <x:c r="H35" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
-      </x:c>
-      <x:c r="I35" s="5" t="str"/>
-      <x:c r="J35" s="5" t="str">
+        <x:v>knowledge.evidence_fragment_or_contract_fact_assertion</x:v>
+      </x:c>
+      <x:c r="I35" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J35" s="5" t="str"/>
+      <x:c r="K35" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K35" s="5" t="str">
+      <x:c r="L35" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L35" s="5" t="str">
+      <x:c r="M35" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M35" s="5" t="str">
+      <x:c r="N35" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N35" s="5" t="str">
+      <x:c r="O35" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O35" s="5" t="str">
+      <x:c r="P35" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P35" s="5" t="str">
+      <x:c r="Q35" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q35" s="5" t="str">
+      <x:c r="R35" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R35" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S35" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T35" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -2303,37 +2361,40 @@
         <x:v>Source until publication</x:v>
       </x:c>
       <x:c r="H36" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
-      </x:c>
-      <x:c r="I36" s="5" t="str"/>
-      <x:c r="J36" s="5" t="str">
+        <x:v>knowledge.contract_finding</x:v>
+      </x:c>
+      <x:c r="I36" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J36" s="5" t="str"/>
+      <x:c r="K36" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K36" s="5" t="str">
+      <x:c r="L36" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L36" s="5" t="str">
+      <x:c r="M36" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M36" s="5" t="str">
+      <x:c r="N36" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N36" s="5" t="str">
+      <x:c r="O36" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O36" s="5" t="str">
+      <x:c r="P36" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P36" s="5" t="str">
+      <x:c r="Q36" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q36" s="5" t="str">
+      <x:c r="R36" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R36" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S36" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T36" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -2360,37 +2421,40 @@
         <x:v>Source until publication</x:v>
       </x:c>
       <x:c r="H37" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
-      </x:c>
-      <x:c r="I37" s="5" t="str"/>
-      <x:c r="J37" s="5" t="str">
+        <x:v>knowledge.value_driver_or_commercial_lever</x:v>
+      </x:c>
+      <x:c r="I37" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J37" s="5" t="str"/>
+      <x:c r="K37" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K37" s="5" t="str">
+      <x:c r="L37" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L37" s="5" t="str">
+      <x:c r="M37" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M37" s="5" t="str">
+      <x:c r="N37" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N37" s="5" t="str">
+      <x:c r="O37" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O37" s="5" t="str">
+      <x:c r="P37" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P37" s="5" t="str">
+      <x:c r="Q37" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q37" s="5" t="str">
+      <x:c r="R37" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R37" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S37" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T37" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -2417,37 +2481,40 @@
         <x:v>Source until publication</x:v>
       </x:c>
       <x:c r="H38" s="5" t="str">
-        <x:v>knowledge.contract</x:v>
-      </x:c>
-      <x:c r="I38" s="5" t="str"/>
-      <x:c r="J38" s="5" t="str">
+        <x:v>knowledge.contract_profile</x:v>
+      </x:c>
+      <x:c r="I38" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J38" s="5" t="str"/>
+      <x:c r="K38" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K38" s="5" t="str">
+      <x:c r="L38" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L38" s="5" t="str">
+      <x:c r="M38" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M38" s="5" t="str">
+      <x:c r="N38" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N38" s="5" t="str">
+      <x:c r="O38" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O38" s="5" t="str">
+      <x:c r="P38" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P38" s="5" t="str">
+      <x:c r="Q38" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q38" s="5" t="str">
+      <x:c r="R38" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R38" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S38" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T38" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -2475,34 +2542,35 @@
       </x:c>
       <x:c r="H39" s="5" t="str"/>
       <x:c r="I39" s="5" t="str"/>
-      <x:c r="J39" s="5" t="str">
+      <x:c r="J39" s="5" t="str"/>
+      <x:c r="K39" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K39" s="5" t="str">
+      <x:c r="L39" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L39" s="5" t="str">
+      <x:c r="M39" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M39" s="5" t="str">
+      <x:c r="N39" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N39" s="5" t="str">
+      <x:c r="O39" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O39" s="5" t="str">
+      <x:c r="P39" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P39" s="5" t="str">
+      <x:c r="Q39" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q39" s="5" t="str">
+      <x:c r="R39" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R39" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S39" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T39" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -2530,34 +2598,35 @@
       </x:c>
       <x:c r="H40" s="5" t="str"/>
       <x:c r="I40" s="5" t="str"/>
-      <x:c r="J40" s="5" t="str">
+      <x:c r="J40" s="5" t="str"/>
+      <x:c r="K40" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K40" s="5" t="str">
+      <x:c r="L40" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L40" s="5" t="str">
+      <x:c r="M40" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M40" s="5" t="str">
+      <x:c r="N40" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N40" s="5" t="str">
+      <x:c r="O40" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O40" s="5" t="str">
+      <x:c r="P40" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P40" s="5" t="str">
+      <x:c r="Q40" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q40" s="5" t="str">
+      <x:c r="R40" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R40" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S40" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T40" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -2585,34 +2654,35 @@
       </x:c>
       <x:c r="H41" s="5" t="str"/>
       <x:c r="I41" s="5" t="str"/>
-      <x:c r="J41" s="5" t="str">
+      <x:c r="J41" s="5" t="str"/>
+      <x:c r="K41" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K41" s="5" t="str">
+      <x:c r="L41" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L41" s="5" t="str">
+      <x:c r="M41" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M41" s="5" t="str">
+      <x:c r="N41" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N41" s="5" t="str">
+      <x:c r="O41" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O41" s="5" t="str">
+      <x:c r="P41" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P41" s="5" t="str">
+      <x:c r="Q41" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q41" s="5" t="str">
+      <x:c r="R41" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R41" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S41" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T41" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -2640,34 +2710,35 @@
       </x:c>
       <x:c r="H42" s="5" t="str"/>
       <x:c r="I42" s="5" t="str"/>
-      <x:c r="J42" s="5" t="str">
+      <x:c r="J42" s="5" t="str"/>
+      <x:c r="K42" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K42" s="5" t="str">
+      <x:c r="L42" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L42" s="5" t="str">
+      <x:c r="M42" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M42" s="5" t="str">
+      <x:c r="N42" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N42" s="5" t="str">
+      <x:c r="O42" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O42" s="5" t="str">
+      <x:c r="P42" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P42" s="5" t="str">
+      <x:c r="Q42" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q42" s="5" t="str">
+      <x:c r="R42" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R42" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S42" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T42" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -2695,34 +2766,35 @@
       </x:c>
       <x:c r="H43" s="5" t="str"/>
       <x:c r="I43" s="5" t="str"/>
-      <x:c r="J43" s="5" t="str">
+      <x:c r="J43" s="5" t="str"/>
+      <x:c r="K43" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K43" s="5" t="str">
+      <x:c r="L43" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L43" s="5" t="str">
+      <x:c r="M43" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M43" s="5" t="str">
+      <x:c r="N43" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N43" s="5" t="str">
+      <x:c r="O43" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O43" s="5" t="str">
+      <x:c r="P43" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P43" s="5" t="str">
+      <x:c r="Q43" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q43" s="5" t="str">
+      <x:c r="R43" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R43" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S43" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T43" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -2751,35 +2823,38 @@
       <x:c r="H44" s="5" t="str">
         <x:v>knowledge.fact</x:v>
       </x:c>
-      <x:c r="I44" s="5" t="str"/>
-      <x:c r="J44" s="5" t="str">
+      <x:c r="I44" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J44" s="5" t="str"/>
+      <x:c r="K44" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K44" s="5" t="str">
+      <x:c r="L44" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L44" s="5" t="str">
+      <x:c r="M44" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M44" s="5" t="str">
+      <x:c r="N44" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N44" s="5" t="str">
+      <x:c r="O44" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O44" s="5" t="str">
+      <x:c r="P44" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P44" s="5" t="str">
+      <x:c r="Q44" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q44" s="5" t="str">
+      <x:c r="R44" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R44" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S44" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T44" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -2807,34 +2882,35 @@
       </x:c>
       <x:c r="H45" s="5" t="str"/>
       <x:c r="I45" s="5" t="str"/>
-      <x:c r="J45" s="5" t="str">
+      <x:c r="J45" s="5" t="str"/>
+      <x:c r="K45" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K45" s="5" t="str">
+      <x:c r="L45" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L45" s="5" t="str">
+      <x:c r="M45" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M45" s="5" t="str">
+      <x:c r="N45" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N45" s="5" t="str">
+      <x:c r="O45" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O45" s="5" t="str">
+      <x:c r="P45" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P45" s="5" t="str">
+      <x:c r="Q45" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q45" s="5" t="str">
+      <x:c r="R45" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R45" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S45" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T45" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -2862,34 +2938,35 @@
       </x:c>
       <x:c r="H46" s="5" t="str"/>
       <x:c r="I46" s="5" t="str"/>
-      <x:c r="J46" s="5" t="str">
+      <x:c r="J46" s="5" t="str"/>
+      <x:c r="K46" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K46" s="5" t="str">
+      <x:c r="L46" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L46" s="5" t="str">
+      <x:c r="M46" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M46" s="5" t="str">
+      <x:c r="N46" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N46" s="5" t="str">
+      <x:c r="O46" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O46" s="5" t="str">
+      <x:c r="P46" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P46" s="5" t="str">
+      <x:c r="Q46" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q46" s="5" t="str">
+      <x:c r="R46" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R46" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S46" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T46" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -2917,34 +2994,35 @@
       </x:c>
       <x:c r="H47" s="5" t="str"/>
       <x:c r="I47" s="5" t="str"/>
-      <x:c r="J47" s="5" t="str">
+      <x:c r="J47" s="5" t="str"/>
+      <x:c r="K47" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K47" s="5" t="str">
+      <x:c r="L47" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L47" s="5" t="str">
+      <x:c r="M47" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M47" s="5" t="str">
+      <x:c r="N47" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N47" s="5" t="str">
+      <x:c r="O47" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O47" s="5" t="str">
+      <x:c r="P47" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P47" s="5" t="str">
+      <x:c r="Q47" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q47" s="5" t="str">
+      <x:c r="R47" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R47" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S47" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T47" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -2972,34 +3050,35 @@
       </x:c>
       <x:c r="H48" s="5" t="str"/>
       <x:c r="I48" s="5" t="str"/>
-      <x:c r="J48" s="5" t="str">
+      <x:c r="J48" s="5" t="str"/>
+      <x:c r="K48" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K48" s="5" t="str">
+      <x:c r="L48" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L48" s="5" t="str">
+      <x:c r="M48" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M48" s="5" t="str">
+      <x:c r="N48" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N48" s="5" t="str">
+      <x:c r="O48" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O48" s="5" t="str">
+      <x:c r="P48" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P48" s="5" t="str">
+      <x:c r="Q48" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q48" s="5" t="str">
+      <x:c r="R48" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R48" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S48" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T48" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -3027,34 +3106,35 @@
       </x:c>
       <x:c r="H49" s="5" t="str"/>
       <x:c r="I49" s="5" t="str"/>
-      <x:c r="J49" s="5" t="str">
+      <x:c r="J49" s="5" t="str"/>
+      <x:c r="K49" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K49" s="5" t="str">
+      <x:c r="L49" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L49" s="5" t="str">
+      <x:c r="M49" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M49" s="5" t="str">
+      <x:c r="N49" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N49" s="5" t="str">
+      <x:c r="O49" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O49" s="5" t="str">
+      <x:c r="P49" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P49" s="5" t="str">
+      <x:c r="Q49" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q49" s="5" t="str">
+      <x:c r="R49" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R49" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S49" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T49" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -3081,37 +3161,40 @@
         <x:v>Source until publication</x:v>
       </x:c>
       <x:c r="H50" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
-      </x:c>
-      <x:c r="I50" s="5" t="str"/>
-      <x:c r="J50" s="5" t="str">
+        <x:v>to_be_mapped_after_live_profile</x:v>
+      </x:c>
+      <x:c r="I50" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="J50" s="5" t="str"/>
+      <x:c r="K50" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K50" s="5" t="str">
+      <x:c r="L50" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L50" s="5" t="str">
+      <x:c r="M50" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M50" s="5" t="str">
+      <x:c r="N50" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N50" s="5" t="str">
+      <x:c r="O50" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O50" s="5" t="str">
+      <x:c r="P50" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P50" s="5" t="str">
+      <x:c r="Q50" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q50" s="5" t="str">
+      <x:c r="R50" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R50" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S50" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T50" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -3139,34 +3222,35 @@
       </x:c>
       <x:c r="H51" s="5" t="str"/>
       <x:c r="I51" s="5" t="str"/>
-      <x:c r="J51" s="5" t="str">
+      <x:c r="J51" s="5" t="str"/>
+      <x:c r="K51" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K51" s="5" t="str">
+      <x:c r="L51" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L51" s="5" t="str">
+      <x:c r="M51" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M51" s="5" t="str">
+      <x:c r="N51" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N51" s="5" t="str">
+      <x:c r="O51" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O51" s="5" t="str">
+      <x:c r="P51" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P51" s="5" t="str">
+      <x:c r="Q51" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q51" s="5" t="str">
+      <x:c r="R51" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R51" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S51" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T51" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -3194,34 +3278,35 @@
       </x:c>
       <x:c r="H52" s="5" t="str"/>
       <x:c r="I52" s="5" t="str"/>
-      <x:c r="J52" s="5" t="str">
+      <x:c r="J52" s="5" t="str"/>
+      <x:c r="K52" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K52" s="5" t="str">
+      <x:c r="L52" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L52" s="5" t="str">
+      <x:c r="M52" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M52" s="5" t="str">
+      <x:c r="N52" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N52" s="5" t="str">
+      <x:c r="O52" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O52" s="5" t="str">
+      <x:c r="P52" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P52" s="5" t="str">
+      <x:c r="Q52" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q52" s="5" t="str">
+      <x:c r="R52" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R52" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S52" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T52" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -3249,34 +3334,35 @@
       </x:c>
       <x:c r="H53" s="5" t="str"/>
       <x:c r="I53" s="5" t="str"/>
-      <x:c r="J53" s="5" t="str">
+      <x:c r="J53" s="5" t="str"/>
+      <x:c r="K53" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K53" s="5" t="str">
+      <x:c r="L53" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L53" s="5" t="str">
+      <x:c r="M53" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M53" s="5" t="str">
+      <x:c r="N53" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N53" s="5" t="str">
+      <x:c r="O53" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O53" s="5" t="str">
+      <x:c r="P53" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P53" s="5" t="str">
+      <x:c r="Q53" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q53" s="5" t="str">
+      <x:c r="R53" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R53" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S53" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T53" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -3304,34 +3390,35 @@
       </x:c>
       <x:c r="H54" s="5" t="str"/>
       <x:c r="I54" s="5" t="str"/>
-      <x:c r="J54" s="5" t="str">
+      <x:c r="J54" s="5" t="str"/>
+      <x:c r="K54" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K54" s="5" t="str">
+      <x:c r="L54" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L54" s="5" t="str">
+      <x:c r="M54" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M54" s="5" t="str">
+      <x:c r="N54" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N54" s="5" t="str">
+      <x:c r="O54" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O54" s="5" t="str">
+      <x:c r="P54" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P54" s="5" t="str">
+      <x:c r="Q54" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q54" s="5" t="str">
+      <x:c r="R54" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R54" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S54" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T54" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -3358,37 +3445,40 @@
         <x:v>Source until publication</x:v>
       </x:c>
       <x:c r="H55" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
-      </x:c>
-      <x:c r="I55" s="5" t="str"/>
-      <x:c r="J55" s="5" t="str">
+        <x:v>knowledge.value_flow_step</x:v>
+      </x:c>
+      <x:c r="I55" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J55" s="5" t="str"/>
+      <x:c r="K55" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K55" s="5" t="str">
+      <x:c r="L55" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L55" s="5" t="str">
+      <x:c r="M55" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M55" s="5" t="str">
+      <x:c r="N55" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N55" s="5" t="str">
+      <x:c r="O55" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O55" s="5" t="str">
+      <x:c r="P55" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P55" s="5" t="str">
+      <x:c r="Q55" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q55" s="5" t="str">
+      <x:c r="R55" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R55" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S55" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T55" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -3415,37 +3505,40 @@
         <x:v>Source until publication</x:v>
       </x:c>
       <x:c r="H56" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
-      </x:c>
-      <x:c r="I56" s="5" t="str"/>
-      <x:c r="J56" s="5" t="str">
+        <x:v>knowledge.value_driver_or_lever</x:v>
+      </x:c>
+      <x:c r="I56" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J56" s="5" t="str"/>
+      <x:c r="K56" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K56" s="5" t="str">
+      <x:c r="L56" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L56" s="5" t="str">
+      <x:c r="M56" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M56" s="5" t="str">
+      <x:c r="N56" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N56" s="5" t="str">
+      <x:c r="O56" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O56" s="5" t="str">
+      <x:c r="P56" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P56" s="5" t="str">
+      <x:c r="Q56" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q56" s="5" t="str">
+      <x:c r="R56" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R56" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S56" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T56" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -3472,37 +3565,40 @@
         <x:v>Source until publication</x:v>
       </x:c>
       <x:c r="H57" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
-      </x:c>
-      <x:c r="I57" s="5" t="str"/>
-      <x:c r="J57" s="5" t="str">
+        <x:v>to_be_mapped_after_live_profile</x:v>
+      </x:c>
+      <x:c r="I57" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="J57" s="5" t="str"/>
+      <x:c r="K57" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K57" s="5" t="str">
+      <x:c r="L57" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L57" s="5" t="str">
+      <x:c r="M57" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M57" s="5" t="str">
+      <x:c r="N57" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N57" s="5" t="str">
+      <x:c r="O57" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O57" s="5" t="str">
+      <x:c r="P57" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P57" s="5" t="str">
+      <x:c r="Q57" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q57" s="5" t="str">
+      <x:c r="R57" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R57" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S57" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T57" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -3529,37 +3625,40 @@
         <x:v>Source until publication</x:v>
       </x:c>
       <x:c r="H58" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
-      </x:c>
-      <x:c r="I58" s="5" t="str"/>
-      <x:c r="J58" s="5" t="str">
+        <x:v>knowledge.value_state_or_readiness</x:v>
+      </x:c>
+      <x:c r="I58" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J58" s="5" t="str"/>
+      <x:c r="K58" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K58" s="5" t="str">
+      <x:c r="L58" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L58" s="5" t="str">
+      <x:c r="M58" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M58" s="5" t="str">
+      <x:c r="N58" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N58" s="5" t="str">
+      <x:c r="O58" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O58" s="5" t="str">
+      <x:c r="P58" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P58" s="5" t="str">
+      <x:c r="Q58" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q58" s="5" t="str">
+      <x:c r="R58" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R58" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S58" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T58" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -3586,37 +3685,40 @@
         <x:v>Source until publication</x:v>
       </x:c>
       <x:c r="H59" s="5" t="str">
-        <x:v>knowledge.vendor</x:v>
-      </x:c>
-      <x:c r="I59" s="5" t="str"/>
-      <x:c r="J59" s="5" t="str">
+        <x:v>knowledge.commercial_commitment</x:v>
+      </x:c>
+      <x:c r="I59" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J59" s="5" t="str"/>
+      <x:c r="K59" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K59" s="5" t="str">
+      <x:c r="L59" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L59" s="5" t="str">
+      <x:c r="M59" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M59" s="5" t="str">
+      <x:c r="N59" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N59" s="5" t="str">
+      <x:c r="O59" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O59" s="5" t="str">
+      <x:c r="P59" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P59" s="5" t="str">
+      <x:c r="Q59" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q59" s="5" t="str">
+      <x:c r="R59" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R59" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S59" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T59" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -3644,34 +3746,35 @@
       </x:c>
       <x:c r="H60" s="5" t="str"/>
       <x:c r="I60" s="5" t="str"/>
-      <x:c r="J60" s="5" t="str">
+      <x:c r="J60" s="5" t="str"/>
+      <x:c r="K60" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K60" s="5" t="str">
+      <x:c r="L60" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L60" s="5" t="str">
+      <x:c r="M60" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M60" s="5" t="str">
+      <x:c r="N60" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N60" s="5" t="str">
+      <x:c r="O60" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O60" s="5" t="str">
+      <x:c r="P60" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P60" s="5" t="str">
+      <x:c r="Q60" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q60" s="5" t="str">
+      <x:c r="R60" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R60" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S60" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T60" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -3698,37 +3801,40 @@
         <x:v>Source until publication</x:v>
       </x:c>
       <x:c r="H61" s="5" t="str">
-        <x:v>knowledge.vendor</x:v>
-      </x:c>
-      <x:c r="I61" s="5" t="str"/>
-      <x:c r="J61" s="5" t="str">
+        <x:v>knowledge.proposal_fact_assertion</x:v>
+      </x:c>
+      <x:c r="I61" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J61" s="5" t="str"/>
+      <x:c r="K61" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K61" s="5" t="str">
+      <x:c r="L61" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L61" s="5" t="str">
+      <x:c r="M61" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M61" s="5" t="str">
+      <x:c r="N61" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N61" s="5" t="str">
+      <x:c r="O61" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O61" s="5" t="str">
+      <x:c r="P61" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P61" s="5" t="str">
+      <x:c r="Q61" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q61" s="5" t="str">
+      <x:c r="R61" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R61" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S61" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T61" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -3756,34 +3862,35 @@
       </x:c>
       <x:c r="H62" s="5" t="str"/>
       <x:c r="I62" s="5" t="str"/>
-      <x:c r="J62" s="5" t="str">
+      <x:c r="J62" s="5" t="str"/>
+      <x:c r="K62" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K62" s="5" t="str">
+      <x:c r="L62" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L62" s="5" t="str">
+      <x:c r="M62" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M62" s="5" t="str">
+      <x:c r="N62" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N62" s="5" t="str">
+      <x:c r="O62" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O62" s="5" t="str">
+      <x:c r="P62" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P62" s="5" t="str">
+      <x:c r="Q62" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q62" s="5" t="str">
+      <x:c r="R62" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R62" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S62" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T62" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -3810,37 +3917,40 @@
         <x:v>Source until publication</x:v>
       </x:c>
       <x:c r="H63" s="5" t="str">
-        <x:v>knowledge.vendor</x:v>
-      </x:c>
-      <x:c r="I63" s="5" t="str"/>
-      <x:c r="J63" s="5" t="str">
+        <x:v>knowledge.contract</x:v>
+      </x:c>
+      <x:c r="I63" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J63" s="5" t="str"/>
+      <x:c r="K63" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K63" s="5" t="str">
+      <x:c r="L63" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L63" s="5" t="str">
+      <x:c r="M63" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M63" s="5" t="str">
+      <x:c r="N63" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N63" s="5" t="str">
+      <x:c r="O63" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O63" s="5" t="str">
+      <x:c r="P63" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P63" s="5" t="str">
+      <x:c r="Q63" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q63" s="5" t="str">
+      <x:c r="R63" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R63" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S63" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T63" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -3868,34 +3978,35 @@
       </x:c>
       <x:c r="H64" s="5" t="str"/>
       <x:c r="I64" s="5" t="str"/>
-      <x:c r="J64" s="5" t="str">
+      <x:c r="J64" s="5" t="str"/>
+      <x:c r="K64" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K64" s="5" t="str">
+      <x:c r="L64" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L64" s="5" t="str">
+      <x:c r="M64" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M64" s="5" t="str">
+      <x:c r="N64" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N64" s="5" t="str">
+      <x:c r="O64" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O64" s="5" t="str">
+      <x:c r="P64" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P64" s="5" t="str">
+      <x:c r="Q64" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q64" s="5" t="str">
+      <x:c r="R64" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R64" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S64" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T64" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -3922,37 +4033,38 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H65" s="5" t="str"/>
-      <x:c r="I65" s="5" t="str">
+      <x:c r="I65" s="5" t="str"/>
+      <x:c r="J65" s="5" t="str">
         <x:v>consumption.metric_facts</x:v>
       </x:c>
-      <x:c r="J65" s="5" t="str">
+      <x:c r="K65" s="5" t="str">
         <x:v>Build/refresh projection from active publications; dual-read compare before switching consumers</x:v>
       </x:c>
-      <x:c r="K65" s="5" t="str">
+      <x:c r="L65" s="5" t="str">
         <x:v>Backfill published observations needed for baseline reports and exports</x:v>
       </x:c>
-      <x:c r="L65" s="5" t="str">
+      <x:c r="M65" s="5" t="str">
         <x:v>Required: old module read versus new projection read</x:v>
       </x:c>
-      <x:c r="M65" s="5" t="str">
+      <x:c r="N65" s="5" t="str">
         <x:v>Counts, tenant scope, lineage, period, unit, and headline metric parity</x:v>
       </x:c>
-      <x:c r="N65" s="5" t="str">
+      <x:c r="O65" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="O65" s="5" t="str">
+      <x:c r="P65" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P65" s="5" t="str">
+      <x:c r="Q65" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q65" s="5" t="str">
+      <x:c r="R65" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R65" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S65" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T65" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -3979,37 +4091,38 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H66" s="5" t="str"/>
-      <x:c r="I66" s="5" t="str">
+      <x:c r="I66" s="5" t="str"/>
+      <x:c r="J66" s="5" t="str">
         <x:v>consumption.mart_ai_portfolio</x:v>
       </x:c>
-      <x:c r="J66" s="5" t="str">
+      <x:c r="K66" s="5" t="str">
         <x:v>Build/refresh projection from active publications; dual-read compare before switching consumers</x:v>
       </x:c>
-      <x:c r="K66" s="5" t="str">
+      <x:c r="L66" s="5" t="str">
         <x:v>Backfill published observations needed for baseline reports and exports</x:v>
       </x:c>
-      <x:c r="L66" s="5" t="str">
+      <x:c r="M66" s="5" t="str">
         <x:v>Required: old module read versus new projection read</x:v>
       </x:c>
-      <x:c r="M66" s="5" t="str">
+      <x:c r="N66" s="5" t="str">
         <x:v>Counts, tenant scope, lineage, period, unit, and headline metric parity</x:v>
       </x:c>
-      <x:c r="N66" s="5" t="str">
+      <x:c r="O66" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="O66" s="5" t="str">
+      <x:c r="P66" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P66" s="5" t="str">
+      <x:c r="Q66" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q66" s="5" t="str">
+      <x:c r="R66" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R66" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S66" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T66" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -4036,37 +4149,38 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H67" s="5" t="str"/>
-      <x:c r="I67" s="5" t="str">
+      <x:c r="I67" s="5" t="str"/>
+      <x:c r="J67" s="5" t="str">
         <x:v>consumption.mart_command_center</x:v>
       </x:c>
-      <x:c r="J67" s="5" t="str">
+      <x:c r="K67" s="5" t="str">
         <x:v>Build/refresh projection from active publications; dual-read compare before switching consumers</x:v>
       </x:c>
-      <x:c r="K67" s="5" t="str">
+      <x:c r="L67" s="5" t="str">
         <x:v>Backfill published observations needed for baseline reports and exports</x:v>
       </x:c>
-      <x:c r="L67" s="5" t="str">
+      <x:c r="M67" s="5" t="str">
         <x:v>Required: old module read versus new projection read</x:v>
       </x:c>
-      <x:c r="M67" s="5" t="str">
+      <x:c r="N67" s="5" t="str">
         <x:v>Counts, tenant scope, lineage, period, unit, and headline metric parity</x:v>
       </x:c>
-      <x:c r="N67" s="5" t="str">
+      <x:c r="O67" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="O67" s="5" t="str">
+      <x:c r="P67" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P67" s="5" t="str">
+      <x:c r="Q67" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q67" s="5" t="str">
+      <x:c r="R67" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R67" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S67" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T67" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -4093,37 +4207,38 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H68" s="5" t="str"/>
-      <x:c r="I68" s="5" t="str">
+      <x:c r="I68" s="5" t="str"/>
+      <x:c r="J68" s="5" t="str">
         <x:v>consumption.mart_cxo_actions</x:v>
       </x:c>
-      <x:c r="J68" s="5" t="str">
+      <x:c r="K68" s="5" t="str">
         <x:v>Build/refresh projection from active publications; dual-read compare before switching consumers</x:v>
       </x:c>
-      <x:c r="K68" s="5" t="str">
+      <x:c r="L68" s="5" t="str">
         <x:v>Backfill published observations needed for baseline reports and exports</x:v>
       </x:c>
-      <x:c r="L68" s="5" t="str">
+      <x:c r="M68" s="5" t="str">
         <x:v>Required: old module read versus new projection read</x:v>
       </x:c>
-      <x:c r="M68" s="5" t="str">
+      <x:c r="N68" s="5" t="str">
         <x:v>Counts, tenant scope, lineage, period, unit, and headline metric parity</x:v>
       </x:c>
-      <x:c r="N68" s="5" t="str">
+      <x:c r="O68" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="O68" s="5" t="str">
+      <x:c r="P68" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P68" s="5" t="str">
+      <x:c r="Q68" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q68" s="5" t="str">
+      <x:c r="R68" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R68" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S68" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T68" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -4150,37 +4265,38 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H69" s="5" t="str"/>
-      <x:c r="I69" s="5" t="str">
+      <x:c r="I69" s="5" t="str"/>
+      <x:c r="J69" s="5" t="str">
         <x:v>consumption.evidence_mart_evidence_lineage</x:v>
       </x:c>
-      <x:c r="J69" s="5" t="str">
+      <x:c r="K69" s="5" t="str">
         <x:v>Build/refresh projection from active publications; dual-read compare before switching consumers</x:v>
       </x:c>
-      <x:c r="K69" s="5" t="str">
+      <x:c r="L69" s="5" t="str">
         <x:v>Backfill published observations needed for baseline reports and exports</x:v>
       </x:c>
-      <x:c r="L69" s="5" t="str">
+      <x:c r="M69" s="5" t="str">
         <x:v>Required: old module read versus new projection read</x:v>
       </x:c>
-      <x:c r="M69" s="5" t="str">
+      <x:c r="N69" s="5" t="str">
         <x:v>Counts, tenant scope, lineage, period, unit, and headline metric parity</x:v>
       </x:c>
-      <x:c r="N69" s="5" t="str">
+      <x:c r="O69" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="O69" s="5" t="str">
+      <x:c r="P69" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P69" s="5" t="str">
+      <x:c r="Q69" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q69" s="5" t="str">
+      <x:c r="R69" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R69" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S69" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T69" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -4207,37 +4323,38 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H70" s="5" t="str"/>
-      <x:c r="I70" s="5" t="str">
+      <x:c r="I70" s="5" t="str"/>
+      <x:c r="J70" s="5" t="str">
         <x:v>consumption.program_mart_program_decision_lanes</x:v>
       </x:c>
-      <x:c r="J70" s="5" t="str">
+      <x:c r="K70" s="5" t="str">
         <x:v>Build/refresh projection from active publications; dual-read compare before switching consumers</x:v>
       </x:c>
-      <x:c r="K70" s="5" t="str">
+      <x:c r="L70" s="5" t="str">
         <x:v>Backfill published observations needed for baseline reports and exports</x:v>
       </x:c>
-      <x:c r="L70" s="5" t="str">
+      <x:c r="M70" s="5" t="str">
         <x:v>Required: old module read versus new projection read</x:v>
       </x:c>
-      <x:c r="M70" s="5" t="str">
+      <x:c r="N70" s="5" t="str">
         <x:v>Counts, tenant scope, lineage, period, unit, and headline metric parity</x:v>
       </x:c>
-      <x:c r="N70" s="5" t="str">
+      <x:c r="O70" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="O70" s="5" t="str">
+      <x:c r="P70" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P70" s="5" t="str">
+      <x:c r="Q70" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q70" s="5" t="str">
+      <x:c r="R70" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R70" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S70" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T70" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -4264,37 +4381,38 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H71" s="5" t="str"/>
-      <x:c r="I71" s="5" t="str">
+      <x:c r="I71" s="5" t="str"/>
+      <x:c r="J71" s="5" t="str">
         <x:v>consumption.mart_required_field_gaps</x:v>
       </x:c>
-      <x:c r="J71" s="5" t="str">
+      <x:c r="K71" s="5" t="str">
         <x:v>Build/refresh projection from active publications; dual-read compare before switching consumers</x:v>
       </x:c>
-      <x:c r="K71" s="5" t="str">
+      <x:c r="L71" s="5" t="str">
         <x:v>Backfill published observations needed for baseline reports and exports</x:v>
       </x:c>
-      <x:c r="L71" s="5" t="str">
+      <x:c r="M71" s="5" t="str">
         <x:v>Required: old module read versus new projection read</x:v>
       </x:c>
-      <x:c r="M71" s="5" t="str">
+      <x:c r="N71" s="5" t="str">
         <x:v>Counts, tenant scope, lineage, period, unit, and headline metric parity</x:v>
       </x:c>
-      <x:c r="N71" s="5" t="str">
+      <x:c r="O71" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="O71" s="5" t="str">
+      <x:c r="P71" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P71" s="5" t="str">
+      <x:c r="Q71" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q71" s="5" t="str">
+      <x:c r="R71" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R71" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S71" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T71" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -4321,37 +4439,38 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H72" s="5" t="str"/>
-      <x:c r="I72" s="5" t="str">
-        <x:v>consumption.metric_mart_value_funnel</x:v>
-      </x:c>
+      <x:c r="I72" s="5" t="str"/>
       <x:c r="J72" s="5" t="str">
+        <x:v>consumption.mart_value_funnel</x:v>
+      </x:c>
+      <x:c r="K72" s="5" t="str">
         <x:v>Build/refresh projection from active publications; dual-read compare before switching consumers</x:v>
       </x:c>
-      <x:c r="K72" s="5" t="str">
+      <x:c r="L72" s="5" t="str">
         <x:v>Backfill published observations needed for baseline reports and exports</x:v>
       </x:c>
-      <x:c r="L72" s="5" t="str">
+      <x:c r="M72" s="5" t="str">
         <x:v>Required: old module read versus new projection read</x:v>
       </x:c>
-      <x:c r="M72" s="5" t="str">
+      <x:c r="N72" s="5" t="str">
         <x:v>Counts, tenant scope, lineage, period, unit, and headline metric parity</x:v>
       </x:c>
-      <x:c r="N72" s="5" t="str">
+      <x:c r="O72" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="O72" s="5" t="str">
+      <x:c r="P72" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P72" s="5" t="str">
+      <x:c r="Q72" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q72" s="5" t="str">
+      <x:c r="R72" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R72" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S72" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T72" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -4378,37 +4497,38 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H73" s="5" t="str"/>
-      <x:c r="I73" s="5" t="str">
+      <x:c r="I73" s="5" t="str"/>
+      <x:c r="J73" s="5" t="str">
         <x:v>consumption.metric_measure_results</x:v>
       </x:c>
-      <x:c r="J73" s="5" t="str">
+      <x:c r="K73" s="5" t="str">
         <x:v>Build/refresh projection from active publications; dual-read compare before switching consumers</x:v>
       </x:c>
-      <x:c r="K73" s="5" t="str">
+      <x:c r="L73" s="5" t="str">
         <x:v>Backfill published observations needed for baseline reports and exports</x:v>
       </x:c>
-      <x:c r="L73" s="5" t="str">
+      <x:c r="M73" s="5" t="str">
         <x:v>Required: old module read versus new projection read</x:v>
       </x:c>
-      <x:c r="M73" s="5" t="str">
+      <x:c r="N73" s="5" t="str">
         <x:v>Counts, tenant scope, lineage, period, unit, and headline metric parity</x:v>
       </x:c>
-      <x:c r="N73" s="5" t="str">
+      <x:c r="O73" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="O73" s="5" t="str">
+      <x:c r="P73" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P73" s="5" t="str">
+      <x:c r="Q73" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q73" s="5" t="str">
+      <x:c r="R73" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R73" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S73" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T73" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -4437,35 +4557,38 @@
       <x:c r="H74" s="5" t="str">
         <x:v>knowledge.metric_definition</x:v>
       </x:c>
-      <x:c r="I74" s="5" t="str"/>
-      <x:c r="J74" s="5" t="str">
+      <x:c r="I74" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J74" s="5" t="str"/>
+      <x:c r="K74" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K74" s="5" t="str">
+      <x:c r="L74" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L74" s="5" t="str">
+      <x:c r="M74" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M74" s="5" t="str">
+      <x:c r="N74" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N74" s="5" t="str">
+      <x:c r="O74" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O74" s="5" t="str">
+      <x:c r="P74" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P74" s="5" t="str">
+      <x:c r="Q74" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q74" s="5" t="str">
+      <x:c r="R74" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R74" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S74" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T74" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -4493,34 +4616,35 @@
       </x:c>
       <x:c r="H75" s="5" t="str"/>
       <x:c r="I75" s="5" t="str"/>
-      <x:c r="J75" s="5" t="str">
+      <x:c r="J75" s="5" t="str"/>
+      <x:c r="K75" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K75" s="5" t="str">
+      <x:c r="L75" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L75" s="5" t="str">
+      <x:c r="M75" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M75" s="5" t="str">
+      <x:c r="N75" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N75" s="5" t="str">
+      <x:c r="O75" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O75" s="5" t="str">
+      <x:c r="P75" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P75" s="5" t="str">
+      <x:c r="Q75" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q75" s="5" t="str">
+      <x:c r="R75" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R75" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S75" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T75" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -4548,34 +4672,35 @@
       </x:c>
       <x:c r="H76" s="5" t="str"/>
       <x:c r="I76" s="5" t="str"/>
-      <x:c r="J76" s="5" t="str">
+      <x:c r="J76" s="5" t="str"/>
+      <x:c r="K76" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K76" s="5" t="str">
+      <x:c r="L76" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L76" s="5" t="str">
+      <x:c r="M76" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M76" s="5" t="str">
+      <x:c r="N76" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N76" s="5" t="str">
+      <x:c r="O76" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O76" s="5" t="str">
+      <x:c r="P76" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P76" s="5" t="str">
+      <x:c r="Q76" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q76" s="5" t="str">
+      <x:c r="R76" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R76" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S76" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T76" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -4603,34 +4728,35 @@
       </x:c>
       <x:c r="H77" s="5" t="str"/>
       <x:c r="I77" s="5" t="str"/>
-      <x:c r="J77" s="5" t="str">
+      <x:c r="J77" s="5" t="str"/>
+      <x:c r="K77" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K77" s="5" t="str">
+      <x:c r="L77" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L77" s="5" t="str">
+      <x:c r="M77" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M77" s="5" t="str">
+      <x:c r="N77" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N77" s="5" t="str">
+      <x:c r="O77" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O77" s="5" t="str">
+      <x:c r="P77" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P77" s="5" t="str">
+      <x:c r="Q77" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q77" s="5" t="str">
+      <x:c r="R77" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R77" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S77" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T77" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -4658,34 +4784,35 @@
       </x:c>
       <x:c r="H78" s="5" t="str"/>
       <x:c r="I78" s="5" t="str"/>
-      <x:c r="J78" s="5" t="str">
+      <x:c r="J78" s="5" t="str"/>
+      <x:c r="K78" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K78" s="5" t="str">
+      <x:c r="L78" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L78" s="5" t="str">
+      <x:c r="M78" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M78" s="5" t="str">
+      <x:c r="N78" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N78" s="5" t="str">
+      <x:c r="O78" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O78" s="5" t="str">
+      <x:c r="P78" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P78" s="5" t="str">
+      <x:c r="Q78" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q78" s="5" t="str">
+      <x:c r="R78" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R78" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S78" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T78" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -4712,37 +4839,40 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H79" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
-      </x:c>
-      <x:c r="I79" s="5" t="str"/>
-      <x:c r="J79" s="5" t="str">
+        <x:v>to_be_mapped_after_live_profile</x:v>
+      </x:c>
+      <x:c r="I79" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="J79" s="5" t="str"/>
+      <x:c r="K79" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K79" s="5" t="str">
+      <x:c r="L79" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L79" s="5" t="str">
+      <x:c r="M79" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M79" s="5" t="str">
+      <x:c r="N79" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N79" s="5" t="str">
+      <x:c r="O79" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O79" s="5" t="str">
+      <x:c r="P79" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P79" s="5" t="str">
+      <x:c r="Q79" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q79" s="5" t="str">
+      <x:c r="R79" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R79" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S79" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T79" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -4770,34 +4900,35 @@
       </x:c>
       <x:c r="H80" s="5" t="str"/>
       <x:c r="I80" s="5" t="str"/>
-      <x:c r="J80" s="5" t="str">
+      <x:c r="J80" s="5" t="str"/>
+      <x:c r="K80" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K80" s="5" t="str">
+      <x:c r="L80" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L80" s="5" t="str">
+      <x:c r="M80" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M80" s="5" t="str">
+      <x:c r="N80" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N80" s="5" t="str">
+      <x:c r="O80" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O80" s="5" t="str">
+      <x:c r="P80" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P80" s="5" t="str">
+      <x:c r="Q80" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q80" s="5" t="str">
+      <x:c r="R80" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R80" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S80" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T80" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -4825,34 +4956,35 @@
       </x:c>
       <x:c r="H81" s="5" t="str"/>
       <x:c r="I81" s="5" t="str"/>
-      <x:c r="J81" s="5" t="str">
+      <x:c r="J81" s="5" t="str"/>
+      <x:c r="K81" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K81" s="5" t="str">
+      <x:c r="L81" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L81" s="5" t="str">
+      <x:c r="M81" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M81" s="5" t="str">
+      <x:c r="N81" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N81" s="5" t="str">
+      <x:c r="O81" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O81" s="5" t="str">
+      <x:c r="P81" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P81" s="5" t="str">
+      <x:c r="Q81" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q81" s="5" t="str">
+      <x:c r="R81" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R81" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S81" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T81" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -4880,34 +5012,35 @@
       </x:c>
       <x:c r="H82" s="5" t="str"/>
       <x:c r="I82" s="5" t="str"/>
-      <x:c r="J82" s="5" t="str">
+      <x:c r="J82" s="5" t="str"/>
+      <x:c r="K82" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K82" s="5" t="str">
+      <x:c r="L82" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L82" s="5" t="str">
+      <x:c r="M82" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M82" s="5" t="str">
+      <x:c r="N82" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N82" s="5" t="str">
+      <x:c r="O82" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O82" s="5" t="str">
+      <x:c r="P82" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P82" s="5" t="str">
+      <x:c r="Q82" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q82" s="5" t="str">
+      <x:c r="R82" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R82" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S82" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T82" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -4934,37 +5067,40 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H83" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
-      </x:c>
-      <x:c r="I83" s="5" t="str"/>
-      <x:c r="J83" s="5" t="str">
+        <x:v>knowledge.action_or_decision</x:v>
+      </x:c>
+      <x:c r="I83" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J83" s="5" t="str"/>
+      <x:c r="K83" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K83" s="5" t="str">
+      <x:c r="L83" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L83" s="5" t="str">
+      <x:c r="M83" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M83" s="5" t="str">
+      <x:c r="N83" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N83" s="5" t="str">
+      <x:c r="O83" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O83" s="5" t="str">
+      <x:c r="P83" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P83" s="5" t="str">
+      <x:c r="Q83" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q83" s="5" t="str">
+      <x:c r="R83" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R83" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S83" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T83" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -4991,37 +5127,40 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H84" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
-      </x:c>
-      <x:c r="I84" s="5" t="str"/>
-      <x:c r="J84" s="5" t="str">
+        <x:v>knowledge.outcome</x:v>
+      </x:c>
+      <x:c r="I84" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J84" s="5" t="str"/>
+      <x:c r="K84" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K84" s="5" t="str">
+      <x:c r="L84" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L84" s="5" t="str">
+      <x:c r="M84" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M84" s="5" t="str">
+      <x:c r="N84" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N84" s="5" t="str">
+      <x:c r="O84" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O84" s="5" t="str">
+      <x:c r="P84" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P84" s="5" t="str">
+      <x:c r="Q84" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q84" s="5" t="str">
+      <x:c r="R84" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R84" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S84" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T84" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -5048,37 +5187,38 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H85" s="5" t="str"/>
-      <x:c r="I85" s="5" t="str">
+      <x:c r="I85" s="5" t="str"/>
+      <x:c r="J85" s="5" t="str">
         <x:v>consumption.context_ai_control_atlas_context_packs</x:v>
       </x:c>
-      <x:c r="J85" s="5" t="str">
+      <x:c r="K85" s="5" t="str">
         <x:v>Build/refresh projection from active publications; dual-read compare before switching consumers</x:v>
       </x:c>
-      <x:c r="K85" s="5" t="str">
+      <x:c r="L85" s="5" t="str">
         <x:v>Backfill published observations needed for baseline reports and exports</x:v>
       </x:c>
-      <x:c r="L85" s="5" t="str">
+      <x:c r="M85" s="5" t="str">
         <x:v>Required: old module read versus new projection read</x:v>
       </x:c>
-      <x:c r="M85" s="5" t="str">
+      <x:c r="N85" s="5" t="str">
         <x:v>Counts, tenant scope, lineage, period, unit, and headline metric parity</x:v>
       </x:c>
-      <x:c r="N85" s="5" t="str">
+      <x:c r="O85" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="O85" s="5" t="str">
+      <x:c r="P85" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P85" s="5" t="str">
+      <x:c r="Q85" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q85" s="5" t="str">
+      <x:c r="R85" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R85" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S85" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T85" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -5105,37 +5245,40 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H86" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
-      </x:c>
-      <x:c r="I86" s="5" t="str"/>
-      <x:c r="J86" s="5" t="str">
+        <x:v>knowledge.metric_observation</x:v>
+      </x:c>
+      <x:c r="I86" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J86" s="5" t="str"/>
+      <x:c r="K86" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K86" s="5" t="str">
+      <x:c r="L86" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L86" s="5" t="str">
+      <x:c r="M86" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M86" s="5" t="str">
+      <x:c r="N86" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N86" s="5" t="str">
+      <x:c r="O86" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O86" s="5" t="str">
+      <x:c r="P86" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P86" s="5" t="str">
+      <x:c r="Q86" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q86" s="5" t="str">
+      <x:c r="R86" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R86" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S86" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T86" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -5162,37 +5305,40 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H87" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
-      </x:c>
-      <x:c r="I87" s="5" t="str"/>
-      <x:c r="J87" s="5" t="str">
+        <x:v>knowledge.fact_assertion</x:v>
+      </x:c>
+      <x:c r="I87" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J87" s="5" t="str"/>
+      <x:c r="K87" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K87" s="5" t="str">
+      <x:c r="L87" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L87" s="5" t="str">
+      <x:c r="M87" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M87" s="5" t="str">
+      <x:c r="N87" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N87" s="5" t="str">
+      <x:c r="O87" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O87" s="5" t="str">
+      <x:c r="P87" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P87" s="5" t="str">
+      <x:c r="Q87" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q87" s="5" t="str">
+      <x:c r="R87" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R87" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S87" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T87" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -5219,37 +5365,40 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H88" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
-      </x:c>
-      <x:c r="I88" s="5" t="str"/>
-      <x:c r="J88" s="5" t="str">
+        <x:v>knowledge.relationship_assertion</x:v>
+      </x:c>
+      <x:c r="I88" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J88" s="5" t="str"/>
+      <x:c r="K88" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K88" s="5" t="str">
+      <x:c r="L88" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L88" s="5" t="str">
+      <x:c r="M88" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M88" s="5" t="str">
+      <x:c r="N88" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N88" s="5" t="str">
+      <x:c r="O88" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O88" s="5" t="str">
+      <x:c r="P88" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P88" s="5" t="str">
+      <x:c r="Q88" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q88" s="5" t="str">
+      <x:c r="R88" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R88" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S88" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T88" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -5276,37 +5425,40 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H89" s="5" t="str">
-        <x:v>knowledge.metric</x:v>
-      </x:c>
-      <x:c r="I89" s="5" t="str"/>
-      <x:c r="J89" s="5" t="str">
+        <x:v>knowledge.metric_observation</x:v>
+      </x:c>
+      <x:c r="I89" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J89" s="5" t="str"/>
+      <x:c r="K89" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K89" s="5" t="str">
+      <x:c r="L89" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L89" s="5" t="str">
+      <x:c r="M89" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M89" s="5" t="str">
+      <x:c r="N89" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N89" s="5" t="str">
+      <x:c r="O89" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O89" s="5" t="str">
+      <x:c r="P89" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P89" s="5" t="str">
+      <x:c r="Q89" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q89" s="5" t="str">
+      <x:c r="R89" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R89" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S89" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T89" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -5333,37 +5485,40 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H90" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
-      </x:c>
-      <x:c r="I90" s="5" t="str"/>
-      <x:c r="J90" s="5" t="str">
+        <x:v>knowledge.evidence</x:v>
+      </x:c>
+      <x:c r="I90" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J90" s="5" t="str"/>
+      <x:c r="K90" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K90" s="5" t="str">
+      <x:c r="L90" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L90" s="5" t="str">
+      <x:c r="M90" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M90" s="5" t="str">
+      <x:c r="N90" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N90" s="5" t="str">
+      <x:c r="O90" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O90" s="5" t="str">
+      <x:c r="P90" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P90" s="5" t="str">
+      <x:c r="Q90" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q90" s="5" t="str">
+      <x:c r="R90" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R90" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S90" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T90" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -5392,35 +5547,38 @@
       <x:c r="H91" s="5" t="str">
         <x:v>knowledge.program</x:v>
       </x:c>
-      <x:c r="I91" s="5" t="str"/>
-      <x:c r="J91" s="5" t="str">
+      <x:c r="I91" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J91" s="5" t="str"/>
+      <x:c r="K91" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K91" s="5" t="str">
+      <x:c r="L91" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L91" s="5" t="str">
+      <x:c r="M91" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M91" s="5" t="str">
+      <x:c r="N91" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N91" s="5" t="str">
+      <x:c r="O91" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O91" s="5" t="str">
+      <x:c r="P91" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P91" s="5" t="str">
+      <x:c r="Q91" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q91" s="5" t="str">
+      <x:c r="R91" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R91" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S91" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T91" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -5447,37 +5605,40 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H92" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
-      </x:c>
-      <x:c r="I92" s="5" t="str"/>
-      <x:c r="J92" s="5" t="str">
+        <x:v>knowledge.metric_observation</x:v>
+      </x:c>
+      <x:c r="I92" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J92" s="5" t="str"/>
+      <x:c r="K92" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K92" s="5" t="str">
+      <x:c r="L92" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L92" s="5" t="str">
+      <x:c r="M92" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M92" s="5" t="str">
+      <x:c r="N92" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N92" s="5" t="str">
+      <x:c r="O92" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O92" s="5" t="str">
+      <x:c r="P92" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P92" s="5" t="str">
+      <x:c r="Q92" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q92" s="5" t="str">
+      <x:c r="R92" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R92" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S92" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T92" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -5505,34 +5666,35 @@
       </x:c>
       <x:c r="H93" s="5" t="str"/>
       <x:c r="I93" s="5" t="str"/>
-      <x:c r="J93" s="5" t="str">
+      <x:c r="J93" s="5" t="str"/>
+      <x:c r="K93" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K93" s="5" t="str">
+      <x:c r="L93" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L93" s="5" t="str">
+      <x:c r="M93" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M93" s="5" t="str">
+      <x:c r="N93" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N93" s="5" t="str">
+      <x:c r="O93" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O93" s="5" t="str">
+      <x:c r="P93" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P93" s="5" t="str">
+      <x:c r="Q93" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q93" s="5" t="str">
+      <x:c r="R93" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R93" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S93" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T93" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -5561,35 +5723,38 @@
       <x:c r="H94" s="5" t="str">
         <x:v>knowledge.risk_control</x:v>
       </x:c>
-      <x:c r="I94" s="5" t="str"/>
-      <x:c r="J94" s="5" t="str">
+      <x:c r="I94" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J94" s="5" t="str"/>
+      <x:c r="K94" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K94" s="5" t="str">
+      <x:c r="L94" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L94" s="5" t="str">
+      <x:c r="M94" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M94" s="5" t="str">
+      <x:c r="N94" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N94" s="5" t="str">
+      <x:c r="O94" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O94" s="5" t="str">
+      <x:c r="P94" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P94" s="5" t="str">
+      <x:c r="Q94" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q94" s="5" t="str">
+      <x:c r="R94" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R94" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S94" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T94" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -5618,35 +5783,38 @@
       <x:c r="H95" s="5" t="str">
         <x:v>knowledge.contract</x:v>
       </x:c>
-      <x:c r="I95" s="5" t="str"/>
-      <x:c r="J95" s="5" t="str">
+      <x:c r="I95" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J95" s="5" t="str"/>
+      <x:c r="K95" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K95" s="5" t="str">
+      <x:c r="L95" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L95" s="5" t="str">
+      <x:c r="M95" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M95" s="5" t="str">
+      <x:c r="N95" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N95" s="5" t="str">
+      <x:c r="O95" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O95" s="5" t="str">
+      <x:c r="P95" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P95" s="5" t="str">
+      <x:c r="Q95" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q95" s="5" t="str">
+      <x:c r="R95" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R95" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S95" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T95" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -5673,37 +5841,40 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H96" s="5" t="str">
-        <x:v>knowledge.risk_control</x:v>
-      </x:c>
-      <x:c r="I96" s="5" t="str"/>
-      <x:c r="J96" s="5" t="str">
+        <x:v>knowledge.metric_observation</x:v>
+      </x:c>
+      <x:c r="I96" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J96" s="5" t="str"/>
+      <x:c r="K96" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K96" s="5" t="str">
+      <x:c r="L96" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L96" s="5" t="str">
+      <x:c r="M96" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M96" s="5" t="str">
+      <x:c r="N96" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N96" s="5" t="str">
+      <x:c r="O96" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O96" s="5" t="str">
+      <x:c r="P96" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P96" s="5" t="str">
+      <x:c r="Q96" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q96" s="5" t="str">
+      <x:c r="R96" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R96" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S96" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T96" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -5730,37 +5901,38 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H97" s="5" t="str"/>
-      <x:c r="I97" s="5" t="str">
+      <x:c r="I97" s="5" t="str"/>
+      <x:c r="J97" s="5" t="str">
         <x:v>consumption.ai_control_tower_lens_mv</x:v>
       </x:c>
-      <x:c r="J97" s="5" t="str">
+      <x:c r="K97" s="5" t="str">
         <x:v>Build/refresh projection from active publications; dual-read compare before switching consumers</x:v>
       </x:c>
-      <x:c r="K97" s="5" t="str">
+      <x:c r="L97" s="5" t="str">
         <x:v>Backfill published observations needed for baseline reports and exports</x:v>
       </x:c>
-      <x:c r="L97" s="5" t="str">
+      <x:c r="M97" s="5" t="str">
         <x:v>Required: old module read versus new projection read</x:v>
       </x:c>
-      <x:c r="M97" s="5" t="str">
+      <x:c r="N97" s="5" t="str">
         <x:v>Counts, tenant scope, lineage, period, unit, and headline metric parity</x:v>
       </x:c>
-      <x:c r="N97" s="5" t="str">
+      <x:c r="O97" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="O97" s="5" t="str">
+      <x:c r="P97" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P97" s="5" t="str">
+      <x:c r="Q97" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q97" s="5" t="str">
+      <x:c r="R97" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R97" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S97" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T97" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -5788,34 +5960,35 @@
       </x:c>
       <x:c r="H98" s="5" t="str"/>
       <x:c r="I98" s="5" t="str"/>
-      <x:c r="J98" s="5" t="str">
+      <x:c r="J98" s="5" t="str"/>
+      <x:c r="K98" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K98" s="5" t="str">
+      <x:c r="L98" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L98" s="5" t="str">
+      <x:c r="M98" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M98" s="5" t="str">
+      <x:c r="N98" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N98" s="5" t="str">
+      <x:c r="O98" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O98" s="5" t="str">
+      <x:c r="P98" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P98" s="5" t="str">
+      <x:c r="Q98" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q98" s="5" t="str">
+      <x:c r="R98" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R98" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S98" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T98" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -5844,35 +6017,38 @@
       <x:c r="H99" s="5" t="str">
         <x:v>knowledge.application</x:v>
       </x:c>
-      <x:c r="I99" s="5" t="str"/>
-      <x:c r="J99" s="5" t="str">
+      <x:c r="I99" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J99" s="5" t="str"/>
+      <x:c r="K99" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K99" s="5" t="str">
+      <x:c r="L99" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L99" s="5" t="str">
+      <x:c r="M99" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M99" s="5" t="str">
+      <x:c r="N99" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N99" s="5" t="str">
+      <x:c r="O99" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O99" s="5" t="str">
+      <x:c r="P99" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P99" s="5" t="str">
+      <x:c r="Q99" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q99" s="5" t="str">
+      <x:c r="R99" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R99" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S99" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T99" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -5900,34 +6076,35 @@
       </x:c>
       <x:c r="H100" s="5" t="str"/>
       <x:c r="I100" s="5" t="str"/>
-      <x:c r="J100" s="5" t="str">
+      <x:c r="J100" s="5" t="str"/>
+      <x:c r="K100" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K100" s="5" t="str">
+      <x:c r="L100" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L100" s="5" t="str">
+      <x:c r="M100" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M100" s="5" t="str">
+      <x:c r="N100" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N100" s="5" t="str">
+      <x:c r="O100" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O100" s="5" t="str">
+      <x:c r="P100" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P100" s="5" t="str">
+      <x:c r="Q100" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q100" s="5" t="str">
+      <x:c r="R100" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R100" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S100" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T100" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -5955,34 +6132,35 @@
       </x:c>
       <x:c r="H101" s="5" t="str"/>
       <x:c r="I101" s="5" t="str"/>
-      <x:c r="J101" s="5" t="str">
+      <x:c r="J101" s="5" t="str"/>
+      <x:c r="K101" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K101" s="5" t="str">
+      <x:c r="L101" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L101" s="5" t="str">
+      <x:c r="M101" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M101" s="5" t="str">
+      <x:c r="N101" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N101" s="5" t="str">
+      <x:c r="O101" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O101" s="5" t="str">
+      <x:c r="P101" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P101" s="5" t="str">
+      <x:c r="Q101" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q101" s="5" t="str">
+      <x:c r="R101" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R101" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S101" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T101" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -6010,34 +6188,35 @@
       </x:c>
       <x:c r="H102" s="5" t="str"/>
       <x:c r="I102" s="5" t="str"/>
-      <x:c r="J102" s="5" t="str">
+      <x:c r="J102" s="5" t="str"/>
+      <x:c r="K102" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K102" s="5" t="str">
+      <x:c r="L102" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L102" s="5" t="str">
+      <x:c r="M102" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M102" s="5" t="str">
+      <x:c r="N102" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N102" s="5" t="str">
+      <x:c r="O102" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O102" s="5" t="str">
+      <x:c r="P102" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P102" s="5" t="str">
+      <x:c r="Q102" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q102" s="5" t="str">
+      <x:c r="R102" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R102" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S102" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T102" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -6065,34 +6244,35 @@
       </x:c>
       <x:c r="H103" s="5" t="str"/>
       <x:c r="I103" s="5" t="str"/>
-      <x:c r="J103" s="5" t="str">
+      <x:c r="J103" s="5" t="str"/>
+      <x:c r="K103" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K103" s="5" t="str">
+      <x:c r="L103" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L103" s="5" t="str">
+      <x:c r="M103" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M103" s="5" t="str">
+      <x:c r="N103" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N103" s="5" t="str">
+      <x:c r="O103" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O103" s="5" t="str">
+      <x:c r="P103" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P103" s="5" t="str">
+      <x:c r="Q103" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q103" s="5" t="str">
+      <x:c r="R103" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R103" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S103" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T103" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -6119,37 +6299,40 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H104" s="5" t="str">
-        <x:v>to_be_mapped</x:v>
-      </x:c>
-      <x:c r="I104" s="5" t="str"/>
-      <x:c r="J104" s="5" t="str">
+        <x:v>to_be_mapped_after_live_profile</x:v>
+      </x:c>
+      <x:c r="I104" s="5" t="str">
+        <x:v>unresolved</x:v>
+      </x:c>
+      <x:c r="J104" s="5" t="str"/>
+      <x:c r="K104" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K104" s="5" t="str">
+      <x:c r="L104" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L104" s="5" t="str">
+      <x:c r="M104" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M104" s="5" t="str">
+      <x:c r="N104" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N104" s="5" t="str">
+      <x:c r="O104" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O104" s="5" t="str">
+      <x:c r="P104" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P104" s="5" t="str">
+      <x:c r="Q104" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q104" s="5" t="str">
+      <x:c r="R104" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R104" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S104" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T104" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -6177,34 +6360,35 @@
       </x:c>
       <x:c r="H105" s="5" t="str"/>
       <x:c r="I105" s="5" t="str"/>
-      <x:c r="J105" s="5" t="str">
+      <x:c r="J105" s="5" t="str"/>
+      <x:c r="K105" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K105" s="5" t="str">
+      <x:c r="L105" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L105" s="5" t="str">
+      <x:c r="M105" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M105" s="5" t="str">
+      <x:c r="N105" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N105" s="5" t="str">
+      <x:c r="O105" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O105" s="5" t="str">
+      <x:c r="P105" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P105" s="5" t="str">
+      <x:c r="Q105" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q105" s="5" t="str">
+      <x:c r="R105" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R105" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S105" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T105" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -6232,34 +6416,35 @@
       </x:c>
       <x:c r="H106" s="5" t="str"/>
       <x:c r="I106" s="5" t="str"/>
-      <x:c r="J106" s="5" t="str">
+      <x:c r="J106" s="5" t="str"/>
+      <x:c r="K106" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K106" s="5" t="str">
+      <x:c r="L106" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L106" s="5" t="str">
+      <x:c r="M106" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M106" s="5" t="str">
+      <x:c r="N106" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N106" s="5" t="str">
+      <x:c r="O106" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O106" s="5" t="str">
+      <x:c r="P106" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P106" s="5" t="str">
+      <x:c r="Q106" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q106" s="5" t="str">
+      <x:c r="R106" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R106" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S106" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T106" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -6287,34 +6472,35 @@
       </x:c>
       <x:c r="H107" s="5" t="str"/>
       <x:c r="I107" s="5" t="str"/>
-      <x:c r="J107" s="5" t="str">
+      <x:c r="J107" s="5" t="str"/>
+      <x:c r="K107" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K107" s="5" t="str">
+      <x:c r="L107" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L107" s="5" t="str">
+      <x:c r="M107" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M107" s="5" t="str">
+      <x:c r="N107" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N107" s="5" t="str">
+      <x:c r="O107" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O107" s="5" t="str">
+      <x:c r="P107" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P107" s="5" t="str">
+      <x:c r="Q107" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q107" s="5" t="str">
+      <x:c r="R107" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R107" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S107" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T107" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -6342,34 +6528,35 @@
       </x:c>
       <x:c r="H108" s="5" t="str"/>
       <x:c r="I108" s="5" t="str"/>
-      <x:c r="J108" s="5" t="str">
+      <x:c r="J108" s="5" t="str"/>
+      <x:c r="K108" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K108" s="5" t="str">
+      <x:c r="L108" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L108" s="5" t="str">
+      <x:c r="M108" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M108" s="5" t="str">
+      <x:c r="N108" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N108" s="5" t="str">
+      <x:c r="O108" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O108" s="5" t="str">
+      <x:c r="P108" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P108" s="5" t="str">
+      <x:c r="Q108" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q108" s="5" t="str">
+      <x:c r="R108" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R108" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S108" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T108" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -6397,34 +6584,35 @@
       </x:c>
       <x:c r="H109" s="5" t="str"/>
       <x:c r="I109" s="5" t="str"/>
-      <x:c r="J109" s="5" t="str">
+      <x:c r="J109" s="5" t="str"/>
+      <x:c r="K109" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K109" s="5" t="str">
+      <x:c r="L109" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L109" s="5" t="str">
+      <x:c r="M109" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M109" s="5" t="str">
+      <x:c r="N109" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N109" s="5" t="str">
+      <x:c r="O109" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O109" s="5" t="str">
+      <x:c r="P109" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P109" s="5" t="str">
+      <x:c r="Q109" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q109" s="5" t="str">
+      <x:c r="R109" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R109" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S109" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T109" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -6451,37 +6639,38 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H110" s="5" t="str"/>
-      <x:c r="I110" s="5" t="str">
+      <x:c r="I110" s="5" t="str"/>
+      <x:c r="J110" s="5" t="str">
         <x:v>consumption.tower_budget_rollups</x:v>
       </x:c>
-      <x:c r="J110" s="5" t="str">
+      <x:c r="K110" s="5" t="str">
         <x:v>Build/refresh projection from active publications; dual-read compare before switching consumers</x:v>
       </x:c>
-      <x:c r="K110" s="5" t="str">
+      <x:c r="L110" s="5" t="str">
         <x:v>Backfill published observations needed for baseline reports and exports</x:v>
       </x:c>
-      <x:c r="L110" s="5" t="str">
+      <x:c r="M110" s="5" t="str">
         <x:v>Required: old module read versus new projection read</x:v>
       </x:c>
-      <x:c r="M110" s="5" t="str">
+      <x:c r="N110" s="5" t="str">
         <x:v>Counts, tenant scope, lineage, period, unit, and headline metric parity</x:v>
       </x:c>
-      <x:c r="N110" s="5" t="str">
+      <x:c r="O110" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="O110" s="5" t="str">
+      <x:c r="P110" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P110" s="5" t="str">
+      <x:c r="Q110" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q110" s="5" t="str">
+      <x:c r="R110" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R110" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S110" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T110" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -6509,34 +6698,35 @@
       </x:c>
       <x:c r="H111" s="5" t="str"/>
       <x:c r="I111" s="5" t="str"/>
-      <x:c r="J111" s="5" t="str">
+      <x:c r="J111" s="5" t="str"/>
+      <x:c r="K111" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K111" s="5" t="str">
+      <x:c r="L111" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L111" s="5" t="str">
+      <x:c r="M111" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M111" s="5" t="str">
+      <x:c r="N111" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N111" s="5" t="str">
+      <x:c r="O111" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O111" s="5" t="str">
+      <x:c r="P111" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P111" s="5" t="str">
+      <x:c r="Q111" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q111" s="5" t="str">
+      <x:c r="R111" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R111" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S111" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T111" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -6564,34 +6754,35 @@
       </x:c>
       <x:c r="H112" s="5" t="str"/>
       <x:c r="I112" s="5" t="str"/>
-      <x:c r="J112" s="5" t="str">
+      <x:c r="J112" s="5" t="str"/>
+      <x:c r="K112" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K112" s="5" t="str">
+      <x:c r="L112" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L112" s="5" t="str">
+      <x:c r="M112" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M112" s="5" t="str">
+      <x:c r="N112" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N112" s="5" t="str">
+      <x:c r="O112" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O112" s="5" t="str">
+      <x:c r="P112" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P112" s="5" t="str">
+      <x:c r="Q112" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q112" s="5" t="str">
+      <x:c r="R112" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R112" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S112" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T112" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -6620,35 +6811,38 @@
       <x:c r="H113" s="5" t="str">
         <x:v>knowledge.application</x:v>
       </x:c>
-      <x:c r="I113" s="5" t="str"/>
-      <x:c r="J113" s="5" t="str">
+      <x:c r="I113" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J113" s="5" t="str"/>
+      <x:c r="K113" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K113" s="5" t="str">
+      <x:c r="L113" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L113" s="5" t="str">
+      <x:c r="M113" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M113" s="5" t="str">
+      <x:c r="N113" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N113" s="5" t="str">
+      <x:c r="O113" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O113" s="5" t="str">
+      <x:c r="P113" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P113" s="5" t="str">
+      <x:c r="Q113" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q113" s="5" t="str">
+      <x:c r="R113" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R113" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S113" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T113" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -6675,37 +6869,38 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H114" s="5" t="str"/>
-      <x:c r="I114" s="5" t="str">
+      <x:c r="I114" s="5" t="str"/>
+      <x:c r="J114" s="5" t="str">
         <x:v>consumption.relationship_tower_cmdb_dependencies</x:v>
       </x:c>
-      <x:c r="J114" s="5" t="str">
+      <x:c r="K114" s="5" t="str">
         <x:v>Build/refresh projection from active publications; dual-read compare before switching consumers</x:v>
       </x:c>
-      <x:c r="K114" s="5" t="str">
+      <x:c r="L114" s="5" t="str">
         <x:v>Backfill published observations needed for baseline reports and exports</x:v>
       </x:c>
-      <x:c r="L114" s="5" t="str">
+      <x:c r="M114" s="5" t="str">
         <x:v>Required: old module read versus new projection read</x:v>
       </x:c>
-      <x:c r="M114" s="5" t="str">
+      <x:c r="N114" s="5" t="str">
         <x:v>Counts, tenant scope, lineage, period, unit, and headline metric parity</x:v>
       </x:c>
-      <x:c r="N114" s="5" t="str">
+      <x:c r="O114" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="O114" s="5" t="str">
+      <x:c r="P114" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P114" s="5" t="str">
+      <x:c r="Q114" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q114" s="5" t="str">
+      <x:c r="R114" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R114" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S114" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T114" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -6732,37 +6927,38 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H115" s="5" t="str"/>
-      <x:c r="I115" s="5" t="str">
+      <x:c r="I115" s="5" t="str"/>
+      <x:c r="J115" s="5" t="str">
         <x:v>consumption.metric_tower_dora_metrics</x:v>
       </x:c>
-      <x:c r="J115" s="5" t="str">
+      <x:c r="K115" s="5" t="str">
         <x:v>Build/refresh projection from active publications; dual-read compare before switching consumers</x:v>
       </x:c>
-      <x:c r="K115" s="5" t="str">
+      <x:c r="L115" s="5" t="str">
         <x:v>Backfill published observations needed for baseline reports and exports</x:v>
       </x:c>
-      <x:c r="L115" s="5" t="str">
+      <x:c r="M115" s="5" t="str">
         <x:v>Required: old module read versus new projection read</x:v>
       </x:c>
-      <x:c r="M115" s="5" t="str">
+      <x:c r="N115" s="5" t="str">
         <x:v>Counts, tenant scope, lineage, period, unit, and headline metric parity</x:v>
       </x:c>
-      <x:c r="N115" s="5" t="str">
+      <x:c r="O115" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="O115" s="5" t="str">
+      <x:c r="P115" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P115" s="5" t="str">
+      <x:c r="Q115" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q115" s="5" t="str">
+      <x:c r="R115" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R115" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S115" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T115" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -6790,34 +6986,35 @@
       </x:c>
       <x:c r="H116" s="5" t="str"/>
       <x:c r="I116" s="5" t="str"/>
-      <x:c r="J116" s="5" t="str">
+      <x:c r="J116" s="5" t="str"/>
+      <x:c r="K116" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K116" s="5" t="str">
+      <x:c r="L116" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L116" s="5" t="str">
+      <x:c r="M116" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M116" s="5" t="str">
+      <x:c r="N116" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N116" s="5" t="str">
+      <x:c r="O116" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O116" s="5" t="str">
+      <x:c r="P116" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P116" s="5" t="str">
+      <x:c r="Q116" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q116" s="5" t="str">
+      <x:c r="R116" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R116" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S116" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T116" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -6845,34 +7042,35 @@
       </x:c>
       <x:c r="H117" s="5" t="str"/>
       <x:c r="I117" s="5" t="str"/>
-      <x:c r="J117" s="5" t="str">
+      <x:c r="J117" s="5" t="str"/>
+      <x:c r="K117" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K117" s="5" t="str">
+      <x:c r="L117" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L117" s="5" t="str">
+      <x:c r="M117" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M117" s="5" t="str">
+      <x:c r="N117" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N117" s="5" t="str">
+      <x:c r="O117" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O117" s="5" t="str">
+      <x:c r="P117" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P117" s="5" t="str">
+      <x:c r="Q117" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q117" s="5" t="str">
+      <x:c r="R117" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R117" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S117" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T117" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -6900,34 +7098,35 @@
       </x:c>
       <x:c r="H118" s="5" t="str"/>
       <x:c r="I118" s="5" t="str"/>
-      <x:c r="J118" s="5" t="str">
+      <x:c r="J118" s="5" t="str"/>
+      <x:c r="K118" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K118" s="5" t="str">
+      <x:c r="L118" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L118" s="5" t="str">
+      <x:c r="M118" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M118" s="5" t="str">
+      <x:c r="N118" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N118" s="5" t="str">
+      <x:c r="O118" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O118" s="5" t="str">
+      <x:c r="P118" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P118" s="5" t="str">
+      <x:c r="Q118" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q118" s="5" t="str">
+      <x:c r="R118" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R118" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S118" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T118" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -6955,34 +7154,35 @@
       </x:c>
       <x:c r="H119" s="5" t="str"/>
       <x:c r="I119" s="5" t="str"/>
-      <x:c r="J119" s="5" t="str">
+      <x:c r="J119" s="5" t="str"/>
+      <x:c r="K119" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K119" s="5" t="str">
+      <x:c r="L119" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L119" s="5" t="str">
+      <x:c r="M119" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M119" s="5" t="str">
+      <x:c r="N119" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N119" s="5" t="str">
+      <x:c r="O119" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O119" s="5" t="str">
+      <x:c r="P119" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P119" s="5" t="str">
+      <x:c r="Q119" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q119" s="5" t="str">
+      <x:c r="R119" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R119" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S119" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T119" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -7010,34 +7210,35 @@
       </x:c>
       <x:c r="H120" s="5" t="str"/>
       <x:c r="I120" s="5" t="str"/>
-      <x:c r="J120" s="5" t="str">
+      <x:c r="J120" s="5" t="str"/>
+      <x:c r="K120" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K120" s="5" t="str">
+      <x:c r="L120" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L120" s="5" t="str">
+      <x:c r="M120" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M120" s="5" t="str">
+      <x:c r="N120" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N120" s="5" t="str">
+      <x:c r="O120" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O120" s="5" t="str">
+      <x:c r="P120" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P120" s="5" t="str">
+      <x:c r="Q120" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q120" s="5" t="str">
+      <x:c r="R120" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R120" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S120" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T120" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -7065,34 +7266,35 @@
       </x:c>
       <x:c r="H121" s="5" t="str"/>
       <x:c r="I121" s="5" t="str"/>
-      <x:c r="J121" s="5" t="str">
+      <x:c r="J121" s="5" t="str"/>
+      <x:c r="K121" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K121" s="5" t="str">
+      <x:c r="L121" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L121" s="5" t="str">
+      <x:c r="M121" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M121" s="5" t="str">
+      <x:c r="N121" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N121" s="5" t="str">
+      <x:c r="O121" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O121" s="5" t="str">
+      <x:c r="P121" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P121" s="5" t="str">
+      <x:c r="Q121" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q121" s="5" t="str">
+      <x:c r="R121" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R121" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S121" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T121" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -7119,37 +7321,38 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H122" s="5" t="str"/>
-      <x:c r="I122" s="5" t="str">
+      <x:c r="I122" s="5" t="str"/>
+      <x:c r="J122" s="5" t="str">
         <x:v>consumption.metric_tower_program_financials</x:v>
       </x:c>
-      <x:c r="J122" s="5" t="str">
+      <x:c r="K122" s="5" t="str">
         <x:v>Build/refresh projection from active publications; dual-read compare before switching consumers</x:v>
       </x:c>
-      <x:c r="K122" s="5" t="str">
+      <x:c r="L122" s="5" t="str">
         <x:v>Backfill published observations needed for baseline reports and exports</x:v>
       </x:c>
-      <x:c r="L122" s="5" t="str">
+      <x:c r="M122" s="5" t="str">
         <x:v>Required: old module read versus new projection read</x:v>
       </x:c>
-      <x:c r="M122" s="5" t="str">
+      <x:c r="N122" s="5" t="str">
         <x:v>Counts, tenant scope, lineage, period, unit, and headline metric parity</x:v>
       </x:c>
-      <x:c r="N122" s="5" t="str">
+      <x:c r="O122" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="O122" s="5" t="str">
+      <x:c r="P122" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P122" s="5" t="str">
+      <x:c r="Q122" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q122" s="5" t="str">
+      <x:c r="R122" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R122" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S122" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T122" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -7177,34 +7380,35 @@
       </x:c>
       <x:c r="H123" s="5" t="str"/>
       <x:c r="I123" s="5" t="str"/>
-      <x:c r="J123" s="5" t="str">
+      <x:c r="J123" s="5" t="str"/>
+      <x:c r="K123" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K123" s="5" t="str">
+      <x:c r="L123" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L123" s="5" t="str">
+      <x:c r="M123" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M123" s="5" t="str">
+      <x:c r="N123" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N123" s="5" t="str">
+      <x:c r="O123" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O123" s="5" t="str">
+      <x:c r="P123" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P123" s="5" t="str">
+      <x:c r="Q123" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q123" s="5" t="str">
+      <x:c r="R123" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R123" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S123" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T123" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -7233,35 +7437,38 @@
       <x:c r="H124" s="5" t="str">
         <x:v>knowledge.vendor</x:v>
       </x:c>
-      <x:c r="I124" s="5" t="str"/>
-      <x:c r="J124" s="5" t="str">
+      <x:c r="I124" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J124" s="5" t="str"/>
+      <x:c r="K124" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K124" s="5" t="str">
+      <x:c r="L124" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L124" s="5" t="str">
+      <x:c r="M124" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M124" s="5" t="str">
+      <x:c r="N124" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N124" s="5" t="str">
+      <x:c r="O124" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O124" s="5" t="str">
+      <x:c r="P124" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P124" s="5" t="str">
+      <x:c r="Q124" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q124" s="5" t="str">
+      <x:c r="R124" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R124" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S124" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T124" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -7289,34 +7496,35 @@
       </x:c>
       <x:c r="H125" s="5" t="str"/>
       <x:c r="I125" s="5" t="str"/>
-      <x:c r="J125" s="5" t="str">
+      <x:c r="J125" s="5" t="str"/>
+      <x:c r="K125" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K125" s="5" t="str">
+      <x:c r="L125" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L125" s="5" t="str">
+      <x:c r="M125" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M125" s="5" t="str">
+      <x:c r="N125" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N125" s="5" t="str">
+      <x:c r="O125" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O125" s="5" t="str">
+      <x:c r="P125" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P125" s="5" t="str">
+      <x:c r="Q125" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q125" s="5" t="str">
+      <x:c r="R125" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R125" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S125" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T125" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -7344,34 +7552,35 @@
       </x:c>
       <x:c r="H126" s="5" t="str"/>
       <x:c r="I126" s="5" t="str"/>
-      <x:c r="J126" s="5" t="str">
+      <x:c r="J126" s="5" t="str"/>
+      <x:c r="K126" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K126" s="5" t="str">
+      <x:c r="L126" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L126" s="5" t="str">
+      <x:c r="M126" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M126" s="5" t="str">
+      <x:c r="N126" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N126" s="5" t="str">
+      <x:c r="O126" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O126" s="5" t="str">
+      <x:c r="P126" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P126" s="5" t="str">
+      <x:c r="Q126" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q126" s="5" t="str">
+      <x:c r="R126" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R126" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S126" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T126" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -7398,37 +7607,38 @@
         <x:v>Tower until publication</x:v>
       </x:c>
       <x:c r="H127" s="5" t="str"/>
-      <x:c r="I127" s="5" t="str">
+      <x:c r="I127" s="5" t="str"/>
+      <x:c r="J127" s="5" t="str">
         <x:v>consumption.metric_tower_vendor_spend</x:v>
       </x:c>
-      <x:c r="J127" s="5" t="str">
+      <x:c r="K127" s="5" t="str">
         <x:v>Build/refresh projection from active publications; dual-read compare before switching consumers</x:v>
       </x:c>
-      <x:c r="K127" s="5" t="str">
+      <x:c r="L127" s="5" t="str">
         <x:v>Backfill published observations needed for baseline reports and exports</x:v>
       </x:c>
-      <x:c r="L127" s="5" t="str">
+      <x:c r="M127" s="5" t="str">
         <x:v>Required: old module read versus new projection read</x:v>
       </x:c>
-      <x:c r="M127" s="5" t="str">
+      <x:c r="N127" s="5" t="str">
         <x:v>Counts, tenant scope, lineage, period, unit, and headline metric parity</x:v>
       </x:c>
-      <x:c r="N127" s="5" t="str">
+      <x:c r="O127" s="5" t="str">
         <x:v>Build stable projection; dual-read compare; switch dashboards/aVa after parity.</x:v>
       </x:c>
-      <x:c r="O127" s="5" t="str">
+      <x:c r="P127" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P127" s="5" t="str">
+      <x:c r="Q127" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q127" s="5" t="str">
+      <x:c r="R127" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R127" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S127" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T127" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -7456,34 +7666,35 @@
       </x:c>
       <x:c r="H128" s="5" t="str"/>
       <x:c r="I128" s="5" t="str"/>
-      <x:c r="J128" s="5" t="str">
+      <x:c r="J128" s="5" t="str"/>
+      <x:c r="K128" s="5" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K128" s="5" t="str">
+      <x:c r="L128" s="5" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L128" s="5" t="str">
+      <x:c r="M128" s="5" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M128" s="5" t="str">
+      <x:c r="N128" s="5" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N128" s="5" t="str">
+      <x:c r="O128" s="5" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O128" s="5" t="str">
+      <x:c r="P128" s="5" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P128" s="5" t="str">
+      <x:c r="Q128" s="5" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q128" s="5" t="str">
+      <x:c r="R128" s="5" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R128" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S128" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T128" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -7512,35 +7723,38 @@
       <x:c r="H129" s="5" t="str">
         <x:v>knowledge.program</x:v>
       </x:c>
-      <x:c r="I129" s="5" t="str"/>
-      <x:c r="J129" s="5" t="str">
+      <x:c r="I129" s="5" t="str">
+        <x:v>provisional</x:v>
+      </x:c>
+      <x:c r="J129" s="5" t="str"/>
+      <x:c r="K129" s="5" t="str">
         <x:v>Map local IDs through governance.object_identity_map; publish reviewed facts through canonical adapter</x:v>
       </x:c>
-      <x:c r="K129" s="5" t="str">
+      <x:c r="L129" s="5" t="str">
         <x:v>Backfill approved/current rows only after stale/superseded filtering</x:v>
       </x:c>
-      <x:c r="L129" s="5" t="str">
+      <x:c r="M129" s="5" t="str">
         <x:v>Required for promoted object family until identity and fact parity pass</x:v>
       </x:c>
-      <x:c r="M129" s="5" t="str">
+      <x:c r="N129" s="5" t="str">
         <x:v>One local object maps to one canonical object or an explicit reviewed many-to-one link</x:v>
       </x:c>
-      <x:c r="N129" s="5" t="str">
+      <x:c r="O129" s="5" t="str">
         <x:v>Backfill identity map; shadow-read canonical projection; switch consumers after reconciliation.</x:v>
       </x:c>
-      <x:c r="O129" s="5" t="str">
+      <x:c r="P129" s="5" t="str">
         <x:v>Revert consumer flag to domain read path; preserve published rows as superseded audit evidence</x:v>
       </x:c>
-      <x:c r="P129" s="5" t="str">
+      <x:c r="Q129" s="5" t="str">
         <x:v>30-60 days after new read primary</x:v>
       </x:c>
-      <x:c r="Q129" s="5" t="str">
+      <x:c r="R129" s="5" t="str">
         <x:v>Keep legacy rows immutable during observation</x:v>
       </x:c>
-      <x:c r="R129" s="5" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S129" s="5" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T129" s="5" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
@@ -7568,34 +7782,35 @@
       </x:c>
       <x:c r="H130" s="6" t="str"/>
       <x:c r="I130" s="6" t="str"/>
-      <x:c r="J130" s="6" t="str">
+      <x:c r="J130" s="6" t="str"/>
+      <x:c r="K130" s="6" t="str">
         <x:v>Preserve current table; add publication outbox only when accepted enterprise facts are emitted</x:v>
       </x:c>
-      <x:c r="K130" s="6" t="str">
+      <x:c r="L130" s="6" t="str">
         <x:v>No backfill until workflow emits accepted publication</x:v>
       </x:c>
-      <x:c r="L130" s="6" t="str">
+      <x:c r="M130" s="6" t="str">
         <x:v>No dual-run until a consumer moves off local reads</x:v>
       </x:c>
-      <x:c r="M130" s="6" t="str">
+      <x:c r="N130" s="6" t="str">
         <x:v>Operational behavior must remain unchanged</x:v>
       </x:c>
-      <x:c r="N130" s="6" t="str">
+      <x:c r="O130" s="6" t="str">
         <x:v>Keep domain owner path; publish outbox if facts are accepted.</x:v>
       </x:c>
-      <x:c r="O130" s="6" t="str">
+      <x:c r="P130" s="6" t="str">
         <x:v>Keep current domain read/write path</x:v>
       </x:c>
-      <x:c r="P130" s="6" t="str">
+      <x:c r="Q130" s="6" t="str">
         <x:v>Not applicable before consumer migration</x:v>
       </x:c>
-      <x:c r="Q130" s="6" t="str">
+      <x:c r="R130" s="6" t="str">
         <x:v>None now</x:v>
       </x:c>
-      <x:c r="R130" s="6" t="str">
-        <x:v>Explicit later approval required; not authorized by this package</x:v>
-      </x:c>
       <x:c r="S130" s="6" t="str">
+        <x:v>Explicit later approval required; not authorized by this package</x:v>
+      </x:c>
+      <x:c r="T130" s="6" t="str">
         <x:v>planning_only</x:v>
       </x:c>
     </x:row>
